--- a/templates/hemodialysis_list_saloc_template.xlsx
+++ b/templates/hemodialysis_list_saloc_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\CB360-Mobile-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55FACF01-AA0A-47FF-B6EB-9AD3F3545B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B09D16B6-75FA-40CF-B50D-BA302C1658AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0525DECB-4297-493F-802D-35D9B36ABCDF}"/>
   </bookViews>
@@ -69,7 +69,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -144,6 +144,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="100"/>
+      <color theme="1"/>
+      <name val="Gill Sans MT"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -153,7 +159,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -358,41 +364,107 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -406,90 +478,38 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -555,195 +575,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1363265</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>180000</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Chaveta à direita 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD6A866B-BCF9-4884-BECE-6E251B8B0093}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2582465" y="13725526"/>
-          <a:ext cx="178810" cy="2000250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rightBrace">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="pt-PT" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1363265</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>180000</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="Chaveta à direita 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3340CCAE-25C4-4A74-A7ED-5A342D4C307E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2582465" y="15868650"/>
-          <a:ext cx="178810" cy="2000250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rightBrace">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="pt-PT" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>186350</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>333375</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="Chaveta à direita 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDE35191-7EAD-4B41-85FF-67600AFC43D1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2587625" y="11582400"/>
-          <a:ext cx="180000" cy="2000250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rightBrace">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="pt-PT" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -789,195 +620,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1363265</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>180000</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="Chaveta à direita 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A17630A5-8323-4FDA-B65F-DC2402B45832}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2582465" y="4114801"/>
-          <a:ext cx="178810" cy="2000250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rightBrace">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="pt-PT" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1363265</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>180000</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="Chaveta à direita 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDFA0FDC-06C8-4874-AB82-42BFD314E72E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2582465" y="6257925"/>
-          <a:ext cx="178810" cy="2000250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rightBrace">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="pt-PT" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>186350</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>333375</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="Chaveta à direita 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14A3F533-C097-47AA-9CCA-23DB2AC51DFE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2587625" y="1971675"/>
-          <a:ext cx="180000" cy="2000250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rightBrace">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="pt-PT" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -1068,6 +710,306 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Imagem 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF6BD3B8-5D7C-452F-8A81-E6070583C923}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2584450" y="4165600"/>
+          <a:ext cx="165100" cy="2032000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Imagem 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7342080-4B15-4CBA-9E7F-3F6E7EDBD2B2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2584450" y="2019300"/>
+          <a:ext cx="165100" cy="2032000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Imagem 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9E5DB93-79F3-454E-8038-F20BC5497E4C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2584450" y="6311900"/>
+          <a:ext cx="165100" cy="2032000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="27" name="Imagem 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2562C752-21F0-4AD0-AEC7-7244E0B99FD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2584450" y="11214100"/>
+          <a:ext cx="165100" cy="2032000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="28" name="Imagem 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{350E7395-F57D-45A1-B8CB-AB5F7FF160B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2584450" y="13360400"/>
+          <a:ext cx="165100" cy="2032000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>165100</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="29" name="Imagem 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9099F3B-CB36-40B4-8319-ADD62C15B126}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2584450" y="15506700"/>
+          <a:ext cx="165100" cy="2032000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1405,60 +1347,60 @@
     <row r="1" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
     </row>
     <row r="9" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="4"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="35"/>
     </row>
     <row r="11" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="5"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="7"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="38"/>
     </row>
     <row r="12" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="8"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="10"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="41"/>
     </row>
     <row r="13" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="11"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="14"/>
+    <row r="14" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="30"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="43"/>
       <c r="F14" s="15" t="s">
         <v>2</v>
       </c>
@@ -1467,88 +1409,88 @@
       <c r="I14" s="16"/>
       <c r="J14" s="17"/>
     </row>
-    <row r="15" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="11"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="14"/>
+    <row r="15" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="30"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="43"/>
       <c r="F15" s="18"/>
       <c r="G15" s="19"/>
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
       <c r="J15" s="20"/>
     </row>
-    <row r="16" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="11"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="14"/>
+    <row r="16" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="30"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="43"/>
       <c r="F16" s="18"/>
       <c r="G16" s="19"/>
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="14"/>
+    <row r="17" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="43"/>
       <c r="F17" s="18"/>
       <c r="G17" s="19"/>
       <c r="H17" s="19"/>
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="11"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="14"/>
+    <row r="18" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="30"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="43"/>
       <c r="F18" s="18"/>
       <c r="G18" s="19"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="11"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="14"/>
+    <row r="19" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="30"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="43"/>
       <c r="F19" s="18"/>
       <c r="G19" s="19"/>
       <c r="H19" s="19"/>
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="21"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="26"/>
+    <row r="20" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="12"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="23"/>
     </row>
     <row r="21" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
     </row>
     <row r="22" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="11"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="14"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="1"/>
       <c r="F22" s="15" t="s">
         <v>3</v>
       </c>
@@ -1558,10 +1500,10 @@
       <c r="J22" s="17"/>
     </row>
     <row r="23" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="11"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="14"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="1"/>
       <c r="F23" s="18"/>
       <c r="G23" s="19"/>
       <c r="H23" s="19"/>
@@ -1569,10 +1511,10 @@
       <c r="J23" s="20"/>
     </row>
     <row r="24" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="11"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="14"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="1"/>
       <c r="F24" s="18"/>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
@@ -1580,10 +1522,10 @@
       <c r="J24" s="20"/>
     </row>
     <row r="25" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="11"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="14"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="1"/>
       <c r="F25" s="18"/>
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
@@ -1591,10 +1533,10 @@
       <c r="J25" s="20"/>
     </row>
     <row r="26" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="11"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="14"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="1"/>
       <c r="F26" s="18"/>
       <c r="G26" s="19"/>
       <c r="H26" s="19"/>
@@ -1602,10 +1544,10 @@
       <c r="J26" s="20"/>
     </row>
     <row r="27" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="11"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="14"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="1"/>
       <c r="F27" s="18"/>
       <c r="G27" s="19"/>
       <c r="H27" s="19"/>
@@ -1613,32 +1555,32 @@
       <c r="J27" s="20"/>
     </row>
     <row r="28" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="11"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="25"/>
-      <c r="J28" s="26"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="23"/>
     </row>
     <row r="29" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
     </row>
     <row r="30" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="21"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="14"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="1"/>
       <c r="F30" s="15" t="s">
         <v>4</v>
       </c>
@@ -1648,10 +1590,10 @@
       <c r="J30" s="17"/>
     </row>
     <row r="31" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="21"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="14"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="1"/>
       <c r="F31" s="18"/>
       <c r="G31" s="19"/>
       <c r="H31" s="19"/>
@@ -1659,10 +1601,10 @@
       <c r="J31" s="20"/>
     </row>
     <row r="32" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="28"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="14"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="1"/>
       <c r="F32" s="18"/>
       <c r="G32" s="19"/>
       <c r="H32" s="19"/>
@@ -1670,10 +1612,10 @@
       <c r="J32" s="20"/>
     </row>
     <row r="33" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="31"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="14"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="1"/>
       <c r="F33" s="18"/>
       <c r="G33" s="19"/>
       <c r="H33" s="19"/>
@@ -1681,10 +1623,10 @@
       <c r="J33" s="20"/>
     </row>
     <row r="34" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="31"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="14"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="1"/>
       <c r="F34" s="18"/>
       <c r="G34" s="19"/>
       <c r="H34" s="19"/>
@@ -1692,10 +1634,10 @@
       <c r="J34" s="20"/>
     </row>
     <row r="35" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="31"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="14"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="1"/>
       <c r="F35" s="18"/>
       <c r="G35" s="19"/>
       <c r="H35" s="19"/>
@@ -1703,159 +1645,159 @@
       <c r="J35" s="20"/>
     </row>
     <row r="36" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="31"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="33"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="24"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="26"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="23"/>
     </row>
     <row r="37" spans="2:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="34"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
     </row>
     <row r="38" spans="2:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="34"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
     </row>
     <row r="39" spans="2:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="35"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="35"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
     </row>
     <row r="40" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="36"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="14"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+      <c r="J40" s="1"/>
     </row>
     <row r="41" spans="2:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="37" t="s">
+      <c r="B41" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C41" s="37"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
-      <c r="J41" s="37"/>
-      <c r="K41" s="38"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="4"/>
     </row>
     <row r="42" spans="2:11" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="39" t="s">
+      <c r="B42" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="39"/>
-      <c r="D42" s="39"/>
-      <c r="E42" s="39"/>
-      <c r="F42" s="39"/>
-      <c r="G42" s="39"/>
-      <c r="H42" s="39"/>
-      <c r="I42" s="39"/>
-      <c r="J42" s="39"/>
-      <c r="K42" s="40"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="5"/>
     </row>
     <row r="43" spans="2:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="41" t="s">
+      <c r="B43" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="41"/>
-      <c r="I43" s="41"/>
-      <c r="J43" s="41"/>
-      <c r="K43" s="42"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="6"/>
     </row>
     <row r="44" spans="2:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
+      <c r="C51" s="42"/>
+      <c r="D51" s="42"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="42"/>
+      <c r="H51" s="42"/>
+      <c r="I51" s="42"/>
+      <c r="J51" s="42"/>
     </row>
     <row r="52" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="53" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-      <c r="J53" s="4"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="34"/>
+      <c r="I53" s="34"/>
+      <c r="J53" s="35"/>
     </row>
     <row r="54" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="5"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="7"/>
+      <c r="B54" s="36"/>
+      <c r="C54" s="37"/>
+      <c r="D54" s="37"/>
+      <c r="E54" s="37"/>
+      <c r="F54" s="37"/>
+      <c r="G54" s="37"/>
+      <c r="H54" s="37"/>
+      <c r="I54" s="37"/>
+      <c r="J54" s="38"/>
     </row>
     <row r="55" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="8"/>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="9"/>
-      <c r="I55" s="9"/>
-      <c r="J55" s="10"/>
+      <c r="B55" s="39"/>
+      <c r="C55" s="40"/>
+      <c r="D55" s="40"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="40"/>
+      <c r="H55" s="40"/>
+      <c r="I55" s="40"/>
+      <c r="J55" s="41"/>
     </row>
     <row r="56" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="11"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="14"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="31"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="1"/>
       <c r="F57" s="15" t="s">
         <v>2</v>
       </c>
@@ -1865,10 +1807,10 @@
       <c r="J57" s="17"/>
     </row>
     <row r="58" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="11"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="14"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="1"/>
       <c r="F58" s="18"/>
       <c r="G58" s="19"/>
       <c r="H58" s="19"/>
@@ -1876,10 +1818,10 @@
       <c r="J58" s="20"/>
     </row>
     <row r="59" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="11"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="14"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="1"/>
       <c r="F59" s="18"/>
       <c r="G59" s="19"/>
       <c r="H59" s="19"/>
@@ -1887,10 +1829,10 @@
       <c r="J59" s="20"/>
     </row>
     <row r="60" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="11"/>
-      <c r="C60" s="12"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="14"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="31"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="1"/>
       <c r="F60" s="18"/>
       <c r="G60" s="19"/>
       <c r="H60" s="19"/>
@@ -1898,10 +1840,10 @@
       <c r="J60" s="20"/>
     </row>
     <row r="61" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="11"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="14"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="1"/>
       <c r="F61" s="18"/>
       <c r="G61" s="19"/>
       <c r="H61" s="19"/>
@@ -1909,10 +1851,10 @@
       <c r="J61" s="20"/>
     </row>
     <row r="62" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="11"/>
-      <c r="C62" s="12"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="14"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="31"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="1"/>
       <c r="F62" s="18"/>
       <c r="G62" s="19"/>
       <c r="H62" s="19"/>
@@ -1920,32 +1862,32 @@
       <c r="J62" s="20"/>
     </row>
     <row r="63" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="21"/>
-      <c r="C63" s="22"/>
-      <c r="D63" s="23"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="24"/>
-      <c r="G63" s="25"/>
-      <c r="H63" s="25"/>
-      <c r="I63" s="25"/>
-      <c r="J63" s="26"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="14"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="21"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="23"/>
     </row>
     <row r="64" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="27"/>
-      <c r="C64" s="27"/>
-      <c r="D64" s="27"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="14"/>
-      <c r="J64" s="14"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
     </row>
     <row r="65" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="11"/>
-      <c r="C65" s="12"/>
-      <c r="D65" s="13"/>
-      <c r="E65" s="14"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="31"/>
+      <c r="D65" s="32"/>
+      <c r="E65" s="1"/>
       <c r="F65" s="15" t="s">
         <v>3</v>
       </c>
@@ -1955,10 +1897,10 @@
       <c r="J65" s="17"/>
     </row>
     <row r="66" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="11"/>
-      <c r="C66" s="12"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="14"/>
+      <c r="B66" s="30"/>
+      <c r="C66" s="31"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="1"/>
       <c r="F66" s="18"/>
       <c r="G66" s="19"/>
       <c r="H66" s="19"/>
@@ -1966,10 +1908,10 @@
       <c r="J66" s="20"/>
     </row>
     <row r="67" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="11"/>
-      <c r="C67" s="12"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="14"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="32"/>
+      <c r="E67" s="1"/>
       <c r="F67" s="18"/>
       <c r="G67" s="19"/>
       <c r="H67" s="19"/>
@@ -1977,10 +1919,10 @@
       <c r="J67" s="20"/>
     </row>
     <row r="68" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="11"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="14"/>
+      <c r="B68" s="30"/>
+      <c r="C68" s="31"/>
+      <c r="D68" s="32"/>
+      <c r="E68" s="1"/>
       <c r="F68" s="18"/>
       <c r="G68" s="19"/>
       <c r="H68" s="19"/>
@@ -1988,10 +1930,10 @@
       <c r="J68" s="20"/>
     </row>
     <row r="69" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="11"/>
-      <c r="C69" s="12"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="14"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="32"/>
+      <c r="E69" s="1"/>
       <c r="F69" s="18"/>
       <c r="G69" s="19"/>
       <c r="H69" s="19"/>
@@ -1999,10 +1941,10 @@
       <c r="J69" s="20"/>
     </row>
     <row r="70" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="11"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="14"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="1"/>
       <c r="F70" s="18"/>
       <c r="G70" s="19"/>
       <c r="H70" s="19"/>
@@ -2010,32 +1952,32 @@
       <c r="J70" s="20"/>
     </row>
     <row r="71" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="11"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="14"/>
-      <c r="F71" s="24"/>
-      <c r="G71" s="25"/>
-      <c r="H71" s="25"/>
-      <c r="I71" s="25"/>
-      <c r="J71" s="26"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="31"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="23"/>
     </row>
     <row r="72" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="27"/>
-      <c r="C72" s="27"/>
-      <c r="D72" s="27"/>
-      <c r="E72" s="14"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="14"/>
-      <c r="J72" s="14"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
     </row>
     <row r="73" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="21"/>
-      <c r="C73" s="22"/>
-      <c r="D73" s="23"/>
-      <c r="E73" s="14"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="14"/>
+      <c r="E73" s="1"/>
       <c r="F73" s="15" t="s">
         <v>4</v>
       </c>
@@ -2045,10 +1987,10 @@
       <c r="J73" s="17"/>
     </row>
     <row r="74" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="21"/>
-      <c r="C74" s="22"/>
-      <c r="D74" s="23"/>
-      <c r="E74" s="14"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="14"/>
+      <c r="E74" s="1"/>
       <c r="F74" s="18"/>
       <c r="G74" s="19"/>
       <c r="H74" s="19"/>
@@ -2056,10 +1998,10 @@
       <c r="J74" s="20"/>
     </row>
     <row r="75" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="28"/>
-      <c r="C75" s="29"/>
-      <c r="D75" s="30"/>
-      <c r="E75" s="14"/>
+      <c r="B75" s="24"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="26"/>
+      <c r="E75" s="1"/>
       <c r="F75" s="18"/>
       <c r="G75" s="19"/>
       <c r="H75" s="19"/>
@@ -2067,10 +2009,10 @@
       <c r="J75" s="20"/>
     </row>
     <row r="76" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="31"/>
-      <c r="C76" s="32"/>
-      <c r="D76" s="33"/>
-      <c r="E76" s="14"/>
+      <c r="B76" s="27"/>
+      <c r="C76" s="28"/>
+      <c r="D76" s="29"/>
+      <c r="E76" s="1"/>
       <c r="F76" s="18"/>
       <c r="G76" s="19"/>
       <c r="H76" s="19"/>
@@ -2078,10 +2020,10 @@
       <c r="J76" s="20"/>
     </row>
     <row r="77" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="31"/>
-      <c r="C77" s="32"/>
-      <c r="D77" s="33"/>
-      <c r="E77" s="14"/>
+      <c r="B77" s="27"/>
+      <c r="C77" s="28"/>
+      <c r="D77" s="29"/>
+      <c r="E77" s="1"/>
       <c r="F77" s="18"/>
       <c r="G77" s="19"/>
       <c r="H77" s="19"/>
@@ -2089,10 +2031,10 @@
       <c r="J77" s="20"/>
     </row>
     <row r="78" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B78" s="31"/>
-      <c r="C78" s="32"/>
-      <c r="D78" s="33"/>
-      <c r="E78" s="14"/>
+      <c r="B78" s="27"/>
+      <c r="C78" s="28"/>
+      <c r="D78" s="29"/>
+      <c r="E78" s="1"/>
       <c r="F78" s="18"/>
       <c r="G78" s="19"/>
       <c r="H78" s="19"/>
@@ -2100,141 +2042,124 @@
       <c r="J78" s="20"/>
     </row>
     <row r="79" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="31"/>
-      <c r="C79" s="32"/>
-      <c r="D79" s="33"/>
-      <c r="E79" s="14"/>
-      <c r="F79" s="24"/>
-      <c r="G79" s="25"/>
-      <c r="H79" s="25"/>
-      <c r="I79" s="25"/>
-      <c r="J79" s="26"/>
+      <c r="B79" s="27"/>
+      <c r="C79" s="28"/>
+      <c r="D79" s="29"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="21"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="23"/>
     </row>
     <row r="80" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B80" s="34"/>
-      <c r="C80" s="34"/>
-      <c r="D80" s="34"/>
-      <c r="E80" s="14"/>
-      <c r="F80" s="14"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="14"/>
-      <c r="J80" s="14"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
     </row>
     <row r="81" spans="2:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B81" s="34"/>
-      <c r="C81" s="34"/>
-      <c r="D81" s="34"/>
-      <c r="E81" s="14"/>
-      <c r="F81" s="14"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="14"/>
-      <c r="J81" s="14"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
     </row>
     <row r="82" spans="2:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B82" s="35"/>
-      <c r="C82" s="35"/>
-      <c r="D82" s="35"/>
-      <c r="E82" s="14"/>
-      <c r="F82" s="14"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="14"/>
-      <c r="J82" s="14"/>
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
     </row>
     <row r="83" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="27"/>
-      <c r="C83" s="27"/>
-      <c r="D83" s="27"/>
-      <c r="E83" s="14"/>
-      <c r="F83" s="36"/>
-      <c r="G83" s="36"/>
-      <c r="H83" s="36"/>
-      <c r="I83" s="36"/>
-      <c r="J83" s="14"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="8"/>
+      <c r="J83" s="1"/>
     </row>
     <row r="84" spans="2:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="37" t="s">
+      <c r="B84" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C84" s="37"/>
-      <c r="D84" s="37"/>
-      <c r="E84" s="37"/>
-      <c r="F84" s="37"/>
-      <c r="G84" s="37"/>
-      <c r="H84" s="37"/>
-      <c r="I84" s="37"/>
-      <c r="J84" s="37"/>
-      <c r="K84" s="38"/>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9"/>
+      <c r="E84" s="9"/>
+      <c r="F84" s="9"/>
+      <c r="G84" s="9"/>
+      <c r="H84" s="9"/>
+      <c r="I84" s="9"/>
+      <c r="J84" s="9"/>
+      <c r="K84" s="4"/>
     </row>
     <row r="85" spans="2:11" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="39" t="s">
+      <c r="B85" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C85" s="39"/>
-      <c r="D85" s="39"/>
-      <c r="E85" s="39"/>
-      <c r="F85" s="39"/>
-      <c r="G85" s="39"/>
-      <c r="H85" s="39"/>
-      <c r="I85" s="39"/>
-      <c r="J85" s="39"/>
-      <c r="K85" s="40"/>
+      <c r="C85" s="10"/>
+      <c r="D85" s="10"/>
+      <c r="E85" s="10"/>
+      <c r="F85" s="10"/>
+      <c r="G85" s="10"/>
+      <c r="H85" s="10"/>
+      <c r="I85" s="10"/>
+      <c r="J85" s="10"/>
+      <c r="K85" s="5"/>
     </row>
     <row r="86" spans="2:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="41" t="s">
+      <c r="B86" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C86" s="41"/>
-      <c r="D86" s="41"/>
-      <c r="E86" s="41"/>
-      <c r="F86" s="41"/>
-      <c r="G86" s="41"/>
-      <c r="H86" s="41"/>
-      <c r="I86" s="41"/>
-      <c r="J86" s="41"/>
-      <c r="K86" s="42"/>
+      <c r="C86" s="11"/>
+      <c r="D86" s="11"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="11"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="11"/>
+      <c r="I86" s="11"/>
+      <c r="J86" s="11"/>
+      <c r="K86" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="66">
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="F83:I83"/>
-    <mergeCell ref="B84:J84"/>
-    <mergeCell ref="B85:J85"/>
-    <mergeCell ref="B86:J86"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="F73:J79"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="F65:J71"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="B53:J55"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="F57:J63"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B40:D40"/>
-    <mergeCell ref="F40:I40"/>
-    <mergeCell ref="B41:J41"/>
-    <mergeCell ref="B42:J42"/>
-    <mergeCell ref="B43:J43"/>
+  <mergeCells count="67">
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="B10:J12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:J20"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E14:E20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:J28"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="B51:J51"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B30:D30"/>
@@ -2245,25 +2170,43 @@
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:J28"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B10:J12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:J20"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B40:D40"/>
+    <mergeCell ref="F40:I40"/>
+    <mergeCell ref="B41:J41"/>
+    <mergeCell ref="B42:J42"/>
+    <mergeCell ref="B43:J43"/>
+    <mergeCell ref="B53:J55"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="F57:J63"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="F65:J71"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="F73:J79"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="F83:I83"/>
+    <mergeCell ref="B84:J84"/>
+    <mergeCell ref="B85:J85"/>
+    <mergeCell ref="B86:J86"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/templates/hemodialysis_list_saloc_template.xlsx
+++ b/templates/hemodialysis_list_saloc_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\CB360-Mobile-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B09D16B6-75FA-40CF-B50D-BA302C1658AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE8C3D9-A428-4A11-8E13-2875BB2F08DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0525DECB-4297-493F-802D-35D9B36ABCDF}"/>
   </bookViews>
@@ -713,22 +713,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:colOff>31751</xdr:colOff>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>165100</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="24" name="Imagem 23">
+        <xdr:cNvPr id="33" name="Imagem 32">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF6BD3B8-5D7C-452F-8A81-E6070583C923}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BA63025-0FA5-645C-C274-ADB5CC4B1D2B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -737,7 +737,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -750,8 +750,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2584450" y="4165600"/>
-          <a:ext cx="165100" cy="2032000"/>
+          <a:off x="2616201" y="2019300"/>
+          <a:ext cx="158749" cy="2000250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -760,25 +760,20 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:colOff>31751</xdr:colOff>
+      <xdr:row>21</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>165100</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="158749" cy="2000250"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="25" name="Imagem 24">
+        <xdr:cNvPr id="34" name="Imagem 33">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D7342080-4B15-4CBA-9E7F-3F6E7EDBD2B2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB83EBBF-3E33-43EF-A22C-3ED3B23691C0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -787,7 +782,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -800,8 +795,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2584450" y="2019300"/>
-          <a:ext cx="165100" cy="2032000"/>
+          <a:off x="2616201" y="4165600"/>
+          <a:ext cx="158749" cy="2000250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -809,26 +804,21 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>31751</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>165100</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="158749" cy="2000250"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="26" name="Imagem 25">
+        <xdr:cNvPr id="35" name="Imagem 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9E5DB93-79F3-454E-8038-F20BC5497E4C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC39D507-55A3-4EAA-858E-6BC24BD40920}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -837,7 +827,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -850,8 +840,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2584450" y="6311900"/>
-          <a:ext cx="165100" cy="2032000"/>
+          <a:off x="2616201" y="4165600"/>
+          <a:ext cx="158749" cy="2000250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -859,26 +849,21 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>31751</xdr:colOff>
       <xdr:row>56</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>165100</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="158749" cy="2000250"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="Imagem 26">
+        <xdr:cNvPr id="36" name="Imagem 35">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2562C752-21F0-4AD0-AEC7-7244E0B99FD2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C774F8EE-73D8-486D-966C-BA8CC1B58C85}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -887,7 +872,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -900,8 +885,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2584450" y="11214100"/>
-          <a:ext cx="165100" cy="2032000"/>
+          <a:off x="2616201" y="6311900"/>
+          <a:ext cx="158749" cy="2000250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -909,26 +894,21 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>31751</xdr:colOff>
       <xdr:row>64</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>165100</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="158749" cy="2000250"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="28" name="Imagem 27">
+        <xdr:cNvPr id="37" name="Imagem 36">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{350E7395-F57D-45A1-B8CB-AB5F7FF160B9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{262761B6-58F7-4850-927D-83E869B5079D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -937,7 +917,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -950,8 +930,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2584450" y="13360400"/>
-          <a:ext cx="165100" cy="2032000"/>
+          <a:off x="2616201" y="6311900"/>
+          <a:ext cx="158749" cy="2000250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -959,26 +939,21 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>31751</xdr:colOff>
       <xdr:row>72</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>165100</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="158749" cy="2000250"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="29" name="Imagem 28">
+        <xdr:cNvPr id="38" name="Imagem 37">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C9099F3B-CB36-40B4-8319-ADD62C15B126}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75034987-700B-4752-BCC0-D931E777DB02}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -987,7 +962,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -1000,8 +975,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2584450" y="15506700"/>
-          <a:ext cx="165100" cy="2032000"/>
+          <a:off x="2616201" y="6311900"/>
+          <a:ext cx="158749" cy="2000250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1009,7 +984,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1486,11 +1461,11 @@
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="30"/>
       <c r="C22" s="31"/>
       <c r="D22" s="32"/>
-      <c r="E22" s="1"/>
+      <c r="E22" s="43"/>
       <c r="F22" s="15" t="s">
         <v>3</v>
       </c>
@@ -1499,66 +1474,66 @@
       <c r="I22" s="16"/>
       <c r="J22" s="17"/>
     </row>
-    <row r="23" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="30"/>
       <c r="C23" s="31"/>
       <c r="D23" s="32"/>
-      <c r="E23" s="1"/>
+      <c r="E23" s="43"/>
       <c r="F23" s="18"/>
       <c r="G23" s="19"/>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="30"/>
       <c r="C24" s="31"/>
       <c r="D24" s="32"/>
-      <c r="E24" s="1"/>
+      <c r="E24" s="43"/>
       <c r="F24" s="18"/>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="30"/>
       <c r="C25" s="31"/>
       <c r="D25" s="32"/>
-      <c r="E25" s="1"/>
+      <c r="E25" s="43"/>
       <c r="F25" s="18"/>
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="30"/>
       <c r="C26" s="31"/>
       <c r="D26" s="32"/>
-      <c r="E26" s="1"/>
+      <c r="E26" s="43"/>
       <c r="F26" s="18"/>
       <c r="G26" s="19"/>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="30"/>
       <c r="C27" s="31"/>
       <c r="D27" s="32"/>
-      <c r="E27" s="1"/>
+      <c r="E27" s="43"/>
       <c r="F27" s="18"/>
       <c r="G27" s="19"/>
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="30"/>
       <c r="C28" s="31"/>
       <c r="D28" s="32"/>
-      <c r="E28" s="1"/>
+      <c r="E28" s="43"/>
       <c r="F28" s="21"/>
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
@@ -1576,11 +1551,11 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="12"/>
       <c r="C30" s="13"/>
       <c r="D30" s="14"/>
-      <c r="E30" s="1"/>
+      <c r="E30" s="43"/>
       <c r="F30" s="15" t="s">
         <v>4</v>
       </c>
@@ -1589,66 +1564,66 @@
       <c r="I30" s="16"/>
       <c r="J30" s="17"/>
     </row>
-    <row r="31" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="12"/>
       <c r="C31" s="13"/>
       <c r="D31" s="14"/>
-      <c r="E31" s="1"/>
+      <c r="E31" s="43"/>
       <c r="F31" s="18"/>
       <c r="G31" s="19"/>
       <c r="H31" s="19"/>
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="24"/>
       <c r="C32" s="25"/>
       <c r="D32" s="26"/>
-      <c r="E32" s="1"/>
+      <c r="E32" s="43"/>
       <c r="F32" s="18"/>
       <c r="G32" s="19"/>
       <c r="H32" s="19"/>
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="27"/>
       <c r="C33" s="28"/>
       <c r="D33" s="29"/>
-      <c r="E33" s="1"/>
+      <c r="E33" s="43"/>
       <c r="F33" s="18"/>
       <c r="G33" s="19"/>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="27"/>
       <c r="C34" s="28"/>
       <c r="D34" s="29"/>
-      <c r="E34" s="1"/>
+      <c r="E34" s="43"/>
       <c r="F34" s="18"/>
       <c r="G34" s="19"/>
       <c r="H34" s="19"/>
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="27"/>
       <c r="C35" s="28"/>
       <c r="D35" s="29"/>
-      <c r="E35" s="1"/>
+      <c r="E35" s="43"/>
       <c r="F35" s="18"/>
       <c r="G35" s="19"/>
       <c r="H35" s="19"/>
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="27"/>
       <c r="C36" s="28"/>
       <c r="D36" s="29"/>
-      <c r="E36" s="1"/>
+      <c r="E36" s="43"/>
       <c r="F36" s="21"/>
       <c r="G36" s="22"/>
       <c r="H36" s="22"/>
@@ -1793,11 +1768,11 @@
       <c r="J55" s="41"/>
     </row>
     <row r="56" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="30"/>
       <c r="C57" s="31"/>
       <c r="D57" s="32"/>
-      <c r="E57" s="1"/>
+      <c r="E57" s="43"/>
       <c r="F57" s="15" t="s">
         <v>2</v>
       </c>
@@ -1806,66 +1781,66 @@
       <c r="I57" s="16"/>
       <c r="J57" s="17"/>
     </row>
-    <row r="58" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="30"/>
       <c r="C58" s="31"/>
       <c r="D58" s="32"/>
-      <c r="E58" s="1"/>
+      <c r="E58" s="43"/>
       <c r="F58" s="18"/>
       <c r="G58" s="19"/>
       <c r="H58" s="19"/>
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="30"/>
       <c r="C59" s="31"/>
       <c r="D59" s="32"/>
-      <c r="E59" s="1"/>
+      <c r="E59" s="43"/>
       <c r="F59" s="18"/>
       <c r="G59" s="19"/>
       <c r="H59" s="19"/>
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="30"/>
       <c r="C60" s="31"/>
       <c r="D60" s="32"/>
-      <c r="E60" s="1"/>
+      <c r="E60" s="43"/>
       <c r="F60" s="18"/>
       <c r="G60" s="19"/>
       <c r="H60" s="19"/>
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="30"/>
       <c r="C61" s="31"/>
       <c r="D61" s="32"/>
-      <c r="E61" s="1"/>
+      <c r="E61" s="43"/>
       <c r="F61" s="18"/>
       <c r="G61" s="19"/>
       <c r="H61" s="19"/>
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="30"/>
       <c r="C62" s="31"/>
       <c r="D62" s="32"/>
-      <c r="E62" s="1"/>
+      <c r="E62" s="43"/>
       <c r="F62" s="18"/>
       <c r="G62" s="19"/>
       <c r="H62" s="19"/>
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="12"/>
       <c r="C63" s="13"/>
       <c r="D63" s="14"/>
-      <c r="E63" s="1"/>
+      <c r="E63" s="43"/>
       <c r="F63" s="21"/>
       <c r="G63" s="22"/>
       <c r="H63" s="22"/>
@@ -1883,11 +1858,11 @@
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
     </row>
-    <row r="65" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="30"/>
       <c r="C65" s="31"/>
       <c r="D65" s="32"/>
-      <c r="E65" s="1"/>
+      <c r="E65" s="43"/>
       <c r="F65" s="15" t="s">
         <v>3</v>
       </c>
@@ -1896,66 +1871,66 @@
       <c r="I65" s="16"/>
       <c r="J65" s="17"/>
     </row>
-    <row r="66" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="30"/>
       <c r="C66" s="31"/>
       <c r="D66" s="32"/>
-      <c r="E66" s="1"/>
+      <c r="E66" s="43"/>
       <c r="F66" s="18"/>
       <c r="G66" s="19"/>
       <c r="H66" s="19"/>
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="30"/>
       <c r="C67" s="31"/>
       <c r="D67" s="32"/>
-      <c r="E67" s="1"/>
+      <c r="E67" s="43"/>
       <c r="F67" s="18"/>
       <c r="G67" s="19"/>
       <c r="H67" s="19"/>
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="30"/>
       <c r="C68" s="31"/>
       <c r="D68" s="32"/>
-      <c r="E68" s="1"/>
+      <c r="E68" s="43"/>
       <c r="F68" s="18"/>
       <c r="G68" s="19"/>
       <c r="H68" s="19"/>
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="30"/>
       <c r="C69" s="31"/>
       <c r="D69" s="32"/>
-      <c r="E69" s="1"/>
+      <c r="E69" s="43"/>
       <c r="F69" s="18"/>
       <c r="G69" s="19"/>
       <c r="H69" s="19"/>
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="30"/>
       <c r="C70" s="31"/>
       <c r="D70" s="32"/>
-      <c r="E70" s="1"/>
+      <c r="E70" s="43"/>
       <c r="F70" s="18"/>
       <c r="G70" s="19"/>
       <c r="H70" s="19"/>
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="30"/>
       <c r="C71" s="31"/>
       <c r="D71" s="32"/>
-      <c r="E71" s="1"/>
+      <c r="E71" s="43"/>
       <c r="F71" s="21"/>
       <c r="G71" s="22"/>
       <c r="H71" s="22"/>
@@ -1973,11 +1948,11 @@
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
     </row>
-    <row r="73" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="12"/>
       <c r="C73" s="13"/>
       <c r="D73" s="14"/>
-      <c r="E73" s="1"/>
+      <c r="E73" s="43"/>
       <c r="F73" s="15" t="s">
         <v>4</v>
       </c>
@@ -1986,66 +1961,66 @@
       <c r="I73" s="16"/>
       <c r="J73" s="17"/>
     </row>
-    <row r="74" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="12"/>
       <c r="C74" s="13"/>
       <c r="D74" s="14"/>
-      <c r="E74" s="1"/>
+      <c r="E74" s="43"/>
       <c r="F74" s="18"/>
       <c r="G74" s="19"/>
       <c r="H74" s="19"/>
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="26"/>
-      <c r="E75" s="1"/>
+      <c r="E75" s="43"/>
       <c r="F75" s="18"/>
       <c r="G75" s="19"/>
       <c r="H75" s="19"/>
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="27"/>
       <c r="C76" s="28"/>
       <c r="D76" s="29"/>
-      <c r="E76" s="1"/>
+      <c r="E76" s="43"/>
       <c r="F76" s="18"/>
       <c r="G76" s="19"/>
       <c r="H76" s="19"/>
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="27"/>
       <c r="C77" s="28"/>
       <c r="D77" s="29"/>
-      <c r="E77" s="1"/>
+      <c r="E77" s="43"/>
       <c r="F77" s="18"/>
       <c r="G77" s="19"/>
       <c r="H77" s="19"/>
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="27"/>
       <c r="C78" s="28"/>
       <c r="D78" s="29"/>
-      <c r="E78" s="1"/>
+      <c r="E78" s="43"/>
       <c r="F78" s="18"/>
       <c r="G78" s="19"/>
       <c r="H78" s="19"/>
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="27"/>
       <c r="C79" s="28"/>
       <c r="D79" s="29"/>
-      <c r="E79" s="1"/>
+      <c r="E79" s="43"/>
       <c r="F79" s="21"/>
       <c r="G79" s="22"/>
       <c r="H79" s="22"/>
@@ -2139,7 +2114,7 @@
       <c r="K86" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="72">
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="B10:J12"/>
     <mergeCell ref="B14:D14"/>
@@ -2160,6 +2135,7 @@
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E22:E28"/>
     <mergeCell ref="B51:J51"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B30:D30"/>
@@ -2170,6 +2146,7 @@
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B36:D36"/>
+    <mergeCell ref="E30:E36"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="F40:I40"/>
     <mergeCell ref="B41:J41"/>
@@ -2184,6 +2161,7 @@
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="B62:D62"/>
     <mergeCell ref="B63:D63"/>
+    <mergeCell ref="E57:E63"/>
     <mergeCell ref="B64:D64"/>
     <mergeCell ref="B65:D65"/>
     <mergeCell ref="F65:J71"/>
@@ -2193,6 +2171,7 @@
     <mergeCell ref="B69:D69"/>
     <mergeCell ref="B70:D70"/>
     <mergeCell ref="B71:D71"/>
+    <mergeCell ref="E65:E71"/>
     <mergeCell ref="B72:D72"/>
     <mergeCell ref="B73:D73"/>
     <mergeCell ref="F73:J79"/>
@@ -2202,6 +2181,7 @@
     <mergeCell ref="B77:D77"/>
     <mergeCell ref="B78:D78"/>
     <mergeCell ref="B79:D79"/>
+    <mergeCell ref="E73:E79"/>
     <mergeCell ref="B83:D83"/>
     <mergeCell ref="F83:I83"/>
     <mergeCell ref="B84:J84"/>

--- a/templates/hemodialysis_list_saloc_template.xlsx
+++ b/templates/hemodialysis_list_saloc_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\CB360-Mobile-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DE8C3D9-A428-4A11-8E13-2875BB2F08DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AA98E20-3DEE-47CA-B454-DF52AD56C51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0525DECB-4297-493F-802D-35D9B36ABCDF}"/>
   </bookViews>
@@ -33,6 +33,28 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69,7 +91,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -143,12 +165,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="100"/>
-      <color theme="1"/>
-      <name val="Gill Sans MT"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -379,7 +395,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -508,7 +524,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -575,6 +594,195 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1363265</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>180000</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Chaveta à direita 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD6A866B-BCF9-4884-BECE-6E251B8B0093}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2582465" y="13725526"/>
+          <a:ext cx="178810" cy="2000250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightBrace">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1363265</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>180000</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Chaveta à direita 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3340CCAE-25C4-4A74-A7ED-5A342D4C307E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2582465" y="15868650"/>
+          <a:ext cx="178810" cy="2000250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightBrace">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>186350</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>333375</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Chaveta à direita 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDE35191-7EAD-4B41-85FF-67600AFC43D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2587625" y="11582400"/>
+          <a:ext cx="180000" cy="2000250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightBrace">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -713,22 +921,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>31751</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
+      <xdr:colOff>193966</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>19762</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="33" name="Imagem 32">
+        <xdr:cNvPr id="3" name="Imagem 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BA63025-0FA5-645C-C274-ADB5CC4B1D2B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AD5D157-C7DF-9B08-27F5-6B698ABD70A0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -750,8 +958,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2616201" y="2019300"/>
-          <a:ext cx="158749" cy="2000250"/>
+          <a:off x="2584450" y="2019300"/>
+          <a:ext cx="193966" cy="2020012"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -760,232 +968,71 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>31751</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="158749" cy="2000250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="34" name="Imagem 33">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB83EBBF-3E33-43EF-A22C-3ED3B23691C0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2616201" y="4165600"/>
-          <a:ext cx="158749" cy="2000250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>31751</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="158749" cy="2000250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="35" name="Imagem 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC39D507-55A3-4EAA-858E-6BC24BD40920}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2616201" y="4165600"/>
-          <a:ext cx="158749" cy="2000250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>31751</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="158749" cy="2000250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="36" name="Imagem 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C774F8EE-73D8-486D-966C-BA8CC1B58C85}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2616201" y="6311900"/>
-          <a:ext cx="158749" cy="2000250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>31751</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="158749" cy="2000250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="37" name="Imagem 36">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{262761B6-58F7-4850-927D-83E869B5079D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2616201" y="6311900"/>
-          <a:ext cx="158749" cy="2000250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>31751</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="158749" cy="2000250"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="38" name="Imagem 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{75034987-700B-4752-BCC0-D931E777DB02}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2616201" y="6311900"/>
-          <a:ext cx="158749" cy="2000250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>0</v>
+    <v>5</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+    <k n="CalcOrigin" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1465,7 +1512,9 @@
       <c r="B22" s="30"/>
       <c r="C22" s="31"/>
       <c r="D22" s="32"/>
-      <c r="E22" s="43"/>
+      <c r="E22" s="44" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
       <c r="F22" s="15" t="s">
         <v>3</v>
       </c>
@@ -1478,7 +1527,7 @@
       <c r="B23" s="30"/>
       <c r="C23" s="31"/>
       <c r="D23" s="32"/>
-      <c r="E23" s="43"/>
+      <c r="E23" s="44"/>
       <c r="F23" s="18"/>
       <c r="G23" s="19"/>
       <c r="H23" s="19"/>
@@ -1489,7 +1538,7 @@
       <c r="B24" s="30"/>
       <c r="C24" s="31"/>
       <c r="D24" s="32"/>
-      <c r="E24" s="43"/>
+      <c r="E24" s="44"/>
       <c r="F24" s="18"/>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
@@ -1500,7 +1549,7 @@
       <c r="B25" s="30"/>
       <c r="C25" s="31"/>
       <c r="D25" s="32"/>
-      <c r="E25" s="43"/>
+      <c r="E25" s="44"/>
       <c r="F25" s="18"/>
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
@@ -1511,7 +1560,7 @@
       <c r="B26" s="30"/>
       <c r="C26" s="31"/>
       <c r="D26" s="32"/>
-      <c r="E26" s="43"/>
+      <c r="E26" s="44"/>
       <c r="F26" s="18"/>
       <c r="G26" s="19"/>
       <c r="H26" s="19"/>
@@ -1522,7 +1571,7 @@
       <c r="B27" s="30"/>
       <c r="C27" s="31"/>
       <c r="D27" s="32"/>
-      <c r="E27" s="43"/>
+      <c r="E27" s="44"/>
       <c r="F27" s="18"/>
       <c r="G27" s="19"/>
       <c r="H27" s="19"/>
@@ -1533,7 +1582,7 @@
       <c r="B28" s="30"/>
       <c r="C28" s="31"/>
       <c r="D28" s="32"/>
-      <c r="E28" s="43"/>
+      <c r="E28" s="44"/>
       <c r="F28" s="21"/>
       <c r="G28" s="22"/>
       <c r="H28" s="22"/>
@@ -1555,7 +1604,9 @@
       <c r="B30" s="12"/>
       <c r="C30" s="13"/>
       <c r="D30" s="14"/>
-      <c r="E30" s="43"/>
+      <c r="E30" s="44" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
       <c r="F30" s="15" t="s">
         <v>4</v>
       </c>
@@ -1568,7 +1619,7 @@
       <c r="B31" s="12"/>
       <c r="C31" s="13"/>
       <c r="D31" s="14"/>
-      <c r="E31" s="43"/>
+      <c r="E31" s="44"/>
       <c r="F31" s="18"/>
       <c r="G31" s="19"/>
       <c r="H31" s="19"/>
@@ -1579,7 +1630,7 @@
       <c r="B32" s="24"/>
       <c r="C32" s="25"/>
       <c r="D32" s="26"/>
-      <c r="E32" s="43"/>
+      <c r="E32" s="44"/>
       <c r="F32" s="18"/>
       <c r="G32" s="19"/>
       <c r="H32" s="19"/>
@@ -1590,7 +1641,7 @@
       <c r="B33" s="27"/>
       <c r="C33" s="28"/>
       <c r="D33" s="29"/>
-      <c r="E33" s="43"/>
+      <c r="E33" s="44"/>
       <c r="F33" s="18"/>
       <c r="G33" s="19"/>
       <c r="H33" s="19"/>
@@ -1601,7 +1652,7 @@
       <c r="B34" s="27"/>
       <c r="C34" s="28"/>
       <c r="D34" s="29"/>
-      <c r="E34" s="43"/>
+      <c r="E34" s="44"/>
       <c r="F34" s="18"/>
       <c r="G34" s="19"/>
       <c r="H34" s="19"/>
@@ -1612,7 +1663,7 @@
       <c r="B35" s="27"/>
       <c r="C35" s="28"/>
       <c r="D35" s="29"/>
-      <c r="E35" s="43"/>
+      <c r="E35" s="44"/>
       <c r="F35" s="18"/>
       <c r="G35" s="19"/>
       <c r="H35" s="19"/>
@@ -1623,7 +1674,7 @@
       <c r="B36" s="27"/>
       <c r="C36" s="28"/>
       <c r="D36" s="29"/>
-      <c r="E36" s="43"/>
+      <c r="E36" s="44"/>
       <c r="F36" s="21"/>
       <c r="G36" s="22"/>
       <c r="H36" s="22"/>
@@ -1768,11 +1819,11 @@
       <c r="J55" s="41"/>
     </row>
     <row r="56" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="30"/>
       <c r="C57" s="31"/>
       <c r="D57" s="32"/>
-      <c r="E57" s="43"/>
+      <c r="E57" s="1"/>
       <c r="F57" s="15" t="s">
         <v>2</v>
       </c>
@@ -1781,66 +1832,66 @@
       <c r="I57" s="16"/>
       <c r="J57" s="17"/>
     </row>
-    <row r="58" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="30"/>
       <c r="C58" s="31"/>
       <c r="D58" s="32"/>
-      <c r="E58" s="43"/>
+      <c r="E58" s="1"/>
       <c r="F58" s="18"/>
       <c r="G58" s="19"/>
       <c r="H58" s="19"/>
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="30"/>
       <c r="C59" s="31"/>
       <c r="D59" s="32"/>
-      <c r="E59" s="43"/>
+      <c r="E59" s="1"/>
       <c r="F59" s="18"/>
       <c r="G59" s="19"/>
       <c r="H59" s="19"/>
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B60" s="30"/>
       <c r="C60" s="31"/>
       <c r="D60" s="32"/>
-      <c r="E60" s="43"/>
+      <c r="E60" s="1"/>
       <c r="F60" s="18"/>
       <c r="G60" s="19"/>
       <c r="H60" s="19"/>
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="30"/>
       <c r="C61" s="31"/>
       <c r="D61" s="32"/>
-      <c r="E61" s="43"/>
+      <c r="E61" s="1"/>
       <c r="F61" s="18"/>
       <c r="G61" s="19"/>
       <c r="H61" s="19"/>
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B62" s="30"/>
       <c r="C62" s="31"/>
       <c r="D62" s="32"/>
-      <c r="E62" s="43"/>
+      <c r="E62" s="1"/>
       <c r="F62" s="18"/>
       <c r="G62" s="19"/>
       <c r="H62" s="19"/>
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B63" s="12"/>
       <c r="C63" s="13"/>
       <c r="D63" s="14"/>
-      <c r="E63" s="43"/>
+      <c r="E63" s="1"/>
       <c r="F63" s="21"/>
       <c r="G63" s="22"/>
       <c r="H63" s="22"/>
@@ -1858,11 +1909,11 @@
       <c r="I64" s="1"/>
       <c r="J64" s="1"/>
     </row>
-    <row r="65" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B65" s="30"/>
       <c r="C65" s="31"/>
       <c r="D65" s="32"/>
-      <c r="E65" s="43"/>
+      <c r="E65" s="1"/>
       <c r="F65" s="15" t="s">
         <v>3</v>
       </c>
@@ -1871,66 +1922,66 @@
       <c r="I65" s="16"/>
       <c r="J65" s="17"/>
     </row>
-    <row r="66" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B66" s="30"/>
       <c r="C66" s="31"/>
       <c r="D66" s="32"/>
-      <c r="E66" s="43"/>
+      <c r="E66" s="1"/>
       <c r="F66" s="18"/>
       <c r="G66" s="19"/>
       <c r="H66" s="19"/>
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B67" s="30"/>
       <c r="C67" s="31"/>
       <c r="D67" s="32"/>
-      <c r="E67" s="43"/>
+      <c r="E67" s="1"/>
       <c r="F67" s="18"/>
       <c r="G67" s="19"/>
       <c r="H67" s="19"/>
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B68" s="30"/>
       <c r="C68" s="31"/>
       <c r="D68" s="32"/>
-      <c r="E68" s="43"/>
+      <c r="E68" s="1"/>
       <c r="F68" s="18"/>
       <c r="G68" s="19"/>
       <c r="H68" s="19"/>
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B69" s="30"/>
       <c r="C69" s="31"/>
       <c r="D69" s="32"/>
-      <c r="E69" s="43"/>
+      <c r="E69" s="1"/>
       <c r="F69" s="18"/>
       <c r="G69" s="19"/>
       <c r="H69" s="19"/>
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B70" s="30"/>
       <c r="C70" s="31"/>
       <c r="D70" s="32"/>
-      <c r="E70" s="43"/>
+      <c r="E70" s="1"/>
       <c r="F70" s="18"/>
       <c r="G70" s="19"/>
       <c r="H70" s="19"/>
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B71" s="30"/>
       <c r="C71" s="31"/>
       <c r="D71" s="32"/>
-      <c r="E71" s="43"/>
+      <c r="E71" s="1"/>
       <c r="F71" s="21"/>
       <c r="G71" s="22"/>
       <c r="H71" s="22"/>
@@ -1948,11 +1999,11 @@
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
     </row>
-    <row r="73" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B73" s="12"/>
       <c r="C73" s="13"/>
       <c r="D73" s="14"/>
-      <c r="E73" s="43"/>
+      <c r="E73" s="1"/>
       <c r="F73" s="15" t="s">
         <v>4</v>
       </c>
@@ -1961,66 +2012,66 @@
       <c r="I73" s="16"/>
       <c r="J73" s="17"/>
     </row>
-    <row r="74" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B74" s="12"/>
       <c r="C74" s="13"/>
       <c r="D74" s="14"/>
-      <c r="E74" s="43"/>
+      <c r="E74" s="1"/>
       <c r="F74" s="18"/>
       <c r="G74" s="19"/>
       <c r="H74" s="19"/>
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B75" s="24"/>
       <c r="C75" s="25"/>
       <c r="D75" s="26"/>
-      <c r="E75" s="43"/>
+      <c r="E75" s="1"/>
       <c r="F75" s="18"/>
       <c r="G75" s="19"/>
       <c r="H75" s="19"/>
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B76" s="27"/>
       <c r="C76" s="28"/>
       <c r="D76" s="29"/>
-      <c r="E76" s="43"/>
+      <c r="E76" s="1"/>
       <c r="F76" s="18"/>
       <c r="G76" s="19"/>
       <c r="H76" s="19"/>
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B77" s="27"/>
       <c r="C77" s="28"/>
       <c r="D77" s="29"/>
-      <c r="E77" s="43"/>
+      <c r="E77" s="1"/>
       <c r="F77" s="18"/>
       <c r="G77" s="19"/>
       <c r="H77" s="19"/>
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B78" s="27"/>
       <c r="C78" s="28"/>
       <c r="D78" s="29"/>
-      <c r="E78" s="43"/>
+      <c r="E78" s="1"/>
       <c r="F78" s="18"/>
       <c r="G78" s="19"/>
       <c r="H78" s="19"/>
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B79" s="27"/>
       <c r="C79" s="28"/>
       <c r="D79" s="29"/>
-      <c r="E79" s="43"/>
+      <c r="E79" s="1"/>
       <c r="F79" s="21"/>
       <c r="G79" s="22"/>
       <c r="H79" s="22"/>
@@ -2114,7 +2165,7 @@
       <c r="K86" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="72">
+  <mergeCells count="69">
     <mergeCell ref="B8:J8"/>
     <mergeCell ref="B10:J12"/>
     <mergeCell ref="B14:D14"/>
@@ -2161,7 +2212,6 @@
     <mergeCell ref="B61:D61"/>
     <mergeCell ref="B62:D62"/>
     <mergeCell ref="B63:D63"/>
-    <mergeCell ref="E57:E63"/>
     <mergeCell ref="B64:D64"/>
     <mergeCell ref="B65:D65"/>
     <mergeCell ref="F65:J71"/>
@@ -2171,7 +2221,6 @@
     <mergeCell ref="B69:D69"/>
     <mergeCell ref="B70:D70"/>
     <mergeCell ref="B71:D71"/>
-    <mergeCell ref="E65:E71"/>
     <mergeCell ref="B72:D72"/>
     <mergeCell ref="B73:D73"/>
     <mergeCell ref="F73:J79"/>
@@ -2181,7 +2230,6 @@
     <mergeCell ref="B77:D77"/>
     <mergeCell ref="B78:D78"/>
     <mergeCell ref="B79:D79"/>
-    <mergeCell ref="E73:E79"/>
     <mergeCell ref="B83:D83"/>
     <mergeCell ref="F83:I83"/>
     <mergeCell ref="B84:J84"/>

--- a/templates/hemodialysis_list_saloc_template.xlsx
+++ b/templates/hemodialysis_list_saloc_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\CB360-Mobile-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AA98E20-3DEE-47CA-B454-DF52AD56C51D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0FDE45E-40D9-4B8A-A137-16554A863D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0525DECB-4297-493F-802D-35D9B36ABCDF}"/>
   </bookViews>
@@ -33,28 +33,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
-  <metadataTypes count="1">
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </valueMetadata>
-</metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,74 +391,35 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -494,41 +433,80 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -549,6 +527,156 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>193966</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>19762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Chatveta_06">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B536E5F-4F31-4447-8EBD-B0049ADBE6CB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2584450" y="15506700"/>
+          <a:ext cx="193966" cy="2020012"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>193966</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>13412</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Chatveta_05">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E89DE2E-22CC-47B6-8E07-BB3173BA6B10}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2584450" y="13354050"/>
+          <a:ext cx="193966" cy="2020012"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1263650</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>187616</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>19762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Chatveta_04">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D53BAE35-7148-450C-9A93-F72F303B265B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2578100" y="11214100"/>
+          <a:ext cx="193966" cy="2020012"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -571,7 +699,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -594,195 +722,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1363265</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>180000</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Chaveta à direita 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD6A866B-BCF9-4884-BECE-6E251B8B0093}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2582465" y="13725526"/>
-          <a:ext cx="178810" cy="2000250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rightBrace">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="pt-PT" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1363265</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>180000</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="Chaveta à direita 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3340CCAE-25C4-4A74-A7ED-5A342D4C307E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2582465" y="15868650"/>
-          <a:ext cx="178810" cy="2000250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rightBrace">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="pt-PT" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>186350</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>333375</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="Chaveta à direita 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDE35191-7EAD-4B41-85FF-67600AFC43D1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2587625" y="11582400"/>
-          <a:ext cx="180000" cy="2000250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rightBrace">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="19050">
-          <a:solidFill>
-            <a:schemeClr val="tx1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="pt-PT" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -805,7 +744,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -850,7 +789,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -895,7 +834,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -933,7 +872,7 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagem 2">
+        <xdr:cNvPr id="3" name="Chatveta_01">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AD5D157-C7DF-9B08-27F5-6B698ABD70A0}"/>
@@ -945,7 +884,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -968,71 +907,107 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>213016</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>13412</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Chatveta_02">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D8C5EB4-9652-46D2-93E3-B7A615FE51C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2603500" y="4159250"/>
+          <a:ext cx="193966" cy="2020012"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>213016</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>13412</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Chatveta_03">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B042A2A-D74F-45D0-8D75-BC92055D8E00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2603500" y="6305550"/>
+          <a:ext cx="193966" cy="2020012"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <rv s="0">
-    <v>0</v>
-    <v>5</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1369,138 +1344,138 @@
     <row r="1" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
     </row>
     <row r="9" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="35"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="10"/>
     </row>
     <row r="11" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="36"/>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="37"/>
-      <c r="H11" s="37"/>
-      <c r="I11" s="37"/>
-      <c r="J11" s="38"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="13"/>
     </row>
     <row r="12" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="40"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="41"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="16"/>
     </row>
     <row r="13" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="30"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="15" t="s">
+      <c r="B14" s="17"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16"/>
-      <c r="J14" s="17"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="22"/>
     </row>
     <row r="15" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="30"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19"/>
-      <c r="J15" s="20"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="25"/>
     </row>
     <row r="16" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="30"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="18"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="20"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="25"/>
     </row>
     <row r="17" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="30"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="20"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="25"/>
     </row>
     <row r="18" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="30"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="20"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="25"/>
     </row>
     <row r="19" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="30"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="20"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="25"/>
     </row>
     <row r="20" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="12"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="23"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="28"/>
     </row>
     <row r="21" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -1509,90 +1484,88 @@
       <c r="J21" s="1"/>
     </row>
     <row r="22" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="30"/>
-      <c r="C22" s="31"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="44" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F22" s="15" t="s">
+      <c r="B22" s="17"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="17"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
+      <c r="J22" s="22"/>
     </row>
     <row r="23" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="30"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="19"/>
-      <c r="I23" s="19"/>
-      <c r="J23" s="20"/>
+      <c r="B23" s="17"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="25"/>
     </row>
     <row r="24" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="30"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="20"/>
+      <c r="B24" s="17"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="25"/>
     </row>
     <row r="25" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="30"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="18"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-      <c r="I25" s="19"/>
-      <c r="J25" s="20"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="23"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="25"/>
     </row>
     <row r="26" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="30"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="18"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="20"/>
+      <c r="B26" s="17"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="23"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="25"/>
     </row>
     <row r="27" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="30"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="19"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="20"/>
+      <c r="B27" s="17"/>
+      <c r="C27" s="18"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="23"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="25"/>
     </row>
     <row r="28" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="30"/>
-      <c r="C28" s="31"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="21"/>
-      <c r="G28" s="22"/>
-      <c r="H28" s="22"/>
-      <c r="I28" s="22"/>
-      <c r="J28" s="23"/>
+      <c r="B28" s="17"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="28"/>
     </row>
     <row r="29" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
+      <c r="B29" s="33"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -1601,85 +1574,83 @@
       <c r="J29" s="1"/>
     </row>
     <row r="30" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="12"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="44" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
-      <c r="F30" s="15" t="s">
+      <c r="B30" s="29"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="31"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="G30" s="16"/>
-      <c r="H30" s="16"/>
-      <c r="I30" s="16"/>
-      <c r="J30" s="17"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="22"/>
     </row>
     <row r="31" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="12"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="19"/>
-      <c r="J31" s="20"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="25"/>
     </row>
     <row r="32" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="24"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="26"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="19"/>
-      <c r="J32" s="20"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="36"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="25"/>
     </row>
     <row r="33" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="27"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19"/>
-      <c r="J33" s="20"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="40"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="25"/>
     </row>
     <row r="34" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="27"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="29"/>
-      <c r="E34" s="44"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="20"/>
+      <c r="B34" s="38"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="40"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="25"/>
     </row>
     <row r="35" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="27"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="29"/>
-      <c r="E35" s="44"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="20"/>
+      <c r="B35" s="38"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="25"/>
     </row>
     <row r="36" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="27"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="44"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
-      <c r="J36" s="23"/>
+      <c r="B36" s="38"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="40"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="27"/>
+      <c r="H36" s="27"/>
+      <c r="I36" s="27"/>
+      <c r="J36" s="28"/>
     </row>
     <row r="37" spans="2:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="2"/>
@@ -1715,193 +1686,193 @@
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
+      <c r="B40" s="33"/>
+      <c r="C40" s="33"/>
+      <c r="D40" s="33"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="8"/>
+      <c r="F40" s="41"/>
+      <c r="G40" s="41"/>
+      <c r="H40" s="41"/>
+      <c r="I40" s="41"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="2:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="9" t="s">
+      <c r="B41" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
-      <c r="H41" s="9"/>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
+      <c r="C41" s="42"/>
+      <c r="D41" s="42"/>
+      <c r="E41" s="42"/>
+      <c r="F41" s="42"/>
+      <c r="G41" s="42"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="42"/>
       <c r="K41" s="4"/>
     </row>
     <row r="42" spans="2:11" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="10"/>
-      <c r="I42" s="10"/>
-      <c r="J42" s="10"/>
+      <c r="C42" s="43"/>
+      <c r="D42" s="43"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="43"/>
+      <c r="G42" s="43"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
       <c r="K42" s="5"/>
     </row>
     <row r="43" spans="2:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
+      <c r="C43" s="44"/>
+      <c r="D43" s="44"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44"/>
       <c r="K43" s="6"/>
     </row>
     <row r="44" spans="2:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="42" t="s">
+      <c r="B51" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C51" s="42"/>
-      <c r="D51" s="42"/>
-      <c r="E51" s="42"/>
-      <c r="F51" s="42"/>
-      <c r="G51" s="42"/>
-      <c r="H51" s="42"/>
-      <c r="I51" s="42"/>
-      <c r="J51" s="42"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="7"/>
+      <c r="H51" s="7"/>
+      <c r="I51" s="7"/>
+      <c r="J51" s="7"/>
     </row>
     <row r="52" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="53" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="33" t="s">
+      <c r="B53" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="34"/>
-      <c r="D53" s="34"/>
-      <c r="E53" s="34"/>
-      <c r="F53" s="34"/>
-      <c r="G53" s="34"/>
-      <c r="H53" s="34"/>
-      <c r="I53" s="34"/>
-      <c r="J53" s="35"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="10"/>
     </row>
     <row r="54" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="36"/>
-      <c r="C54" s="37"/>
-      <c r="D54" s="37"/>
-      <c r="E54" s="37"/>
-      <c r="F54" s="37"/>
-      <c r="G54" s="37"/>
-      <c r="H54" s="37"/>
-      <c r="I54" s="37"/>
-      <c r="J54" s="38"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="13"/>
     </row>
     <row r="55" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="39"/>
-      <c r="C55" s="40"/>
-      <c r="D55" s="40"/>
-      <c r="E55" s="40"/>
-      <c r="F55" s="40"/>
-      <c r="G55" s="40"/>
-      <c r="H55" s="40"/>
-      <c r="I55" s="40"/>
-      <c r="J55" s="41"/>
+      <c r="B55" s="14"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="16"/>
     </row>
     <row r="56" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="30"/>
-      <c r="C57" s="31"/>
-      <c r="D57" s="32"/>
+      <c r="B57" s="17"/>
+      <c r="C57" s="18"/>
+      <c r="D57" s="19"/>
       <c r="E57" s="1"/>
-      <c r="F57" s="15" t="s">
+      <c r="F57" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="G57" s="16"/>
-      <c r="H57" s="16"/>
-      <c r="I57" s="16"/>
-      <c r="J57" s="17"/>
+      <c r="G57" s="21"/>
+      <c r="H57" s="21"/>
+      <c r="I57" s="21"/>
+      <c r="J57" s="22"/>
     </row>
     <row r="58" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="30"/>
-      <c r="C58" s="31"/>
-      <c r="D58" s="32"/>
+      <c r="B58" s="17"/>
+      <c r="C58" s="18"/>
+      <c r="D58" s="19"/>
       <c r="E58" s="1"/>
-      <c r="F58" s="18"/>
-      <c r="G58" s="19"/>
-      <c r="H58" s="19"/>
-      <c r="I58" s="19"/>
-      <c r="J58" s="20"/>
+      <c r="F58" s="23"/>
+      <c r="G58" s="24"/>
+      <c r="H58" s="24"/>
+      <c r="I58" s="24"/>
+      <c r="J58" s="25"/>
     </row>
     <row r="59" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="30"/>
-      <c r="C59" s="31"/>
-      <c r="D59" s="32"/>
+      <c r="B59" s="17"/>
+      <c r="C59" s="18"/>
+      <c r="D59" s="19"/>
       <c r="E59" s="1"/>
-      <c r="F59" s="18"/>
-      <c r="G59" s="19"/>
-      <c r="H59" s="19"/>
-      <c r="I59" s="19"/>
-      <c r="J59" s="20"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="24"/>
+      <c r="H59" s="24"/>
+      <c r="I59" s="24"/>
+      <c r="J59" s="25"/>
     </row>
     <row r="60" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="30"/>
-      <c r="C60" s="31"/>
-      <c r="D60" s="32"/>
+      <c r="B60" s="17"/>
+      <c r="C60" s="18"/>
+      <c r="D60" s="19"/>
       <c r="E60" s="1"/>
-      <c r="F60" s="18"/>
-      <c r="G60" s="19"/>
-      <c r="H60" s="19"/>
-      <c r="I60" s="19"/>
-      <c r="J60" s="20"/>
+      <c r="F60" s="23"/>
+      <c r="G60" s="24"/>
+      <c r="H60" s="24"/>
+      <c r="I60" s="24"/>
+      <c r="J60" s="25"/>
     </row>
     <row r="61" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="30"/>
-      <c r="C61" s="31"/>
-      <c r="D61" s="32"/>
+      <c r="B61" s="17"/>
+      <c r="C61" s="18"/>
+      <c r="D61" s="19"/>
       <c r="E61" s="1"/>
-      <c r="F61" s="18"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="19"/>
-      <c r="J61" s="20"/>
+      <c r="F61" s="23"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="24"/>
+      <c r="I61" s="24"/>
+      <c r="J61" s="25"/>
     </row>
     <row r="62" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="30"/>
-      <c r="C62" s="31"/>
-      <c r="D62" s="32"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="18"/>
+      <c r="D62" s="19"/>
       <c r="E62" s="1"/>
-      <c r="F62" s="18"/>
-      <c r="G62" s="19"/>
-      <c r="H62" s="19"/>
-      <c r="I62" s="19"/>
-      <c r="J62" s="20"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="24"/>
+      <c r="I62" s="24"/>
+      <c r="J62" s="25"/>
     </row>
     <row r="63" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="12"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="14"/>
+      <c r="B63" s="29"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="31"/>
       <c r="E63" s="1"/>
-      <c r="F63" s="21"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="22"/>
-      <c r="I63" s="22"/>
-      <c r="J63" s="23"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="27"/>
+      <c r="H63" s="27"/>
+      <c r="I63" s="27"/>
+      <c r="J63" s="28"/>
     </row>
     <row r="64" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
+      <c r="B64" s="33"/>
+      <c r="C64" s="33"/>
+      <c r="D64" s="33"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -1910,88 +1881,88 @@
       <c r="J64" s="1"/>
     </row>
     <row r="65" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="30"/>
-      <c r="C65" s="31"/>
-      <c r="D65" s="32"/>
+      <c r="B65" s="17"/>
+      <c r="C65" s="18"/>
+      <c r="D65" s="19"/>
       <c r="E65" s="1"/>
-      <c r="F65" s="15" t="s">
+      <c r="F65" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="G65" s="16"/>
-      <c r="H65" s="16"/>
-      <c r="I65" s="16"/>
-      <c r="J65" s="17"/>
+      <c r="G65" s="21"/>
+      <c r="H65" s="21"/>
+      <c r="I65" s="21"/>
+      <c r="J65" s="22"/>
     </row>
     <row r="66" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="30"/>
-      <c r="C66" s="31"/>
-      <c r="D66" s="32"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="18"/>
+      <c r="D66" s="19"/>
       <c r="E66" s="1"/>
-      <c r="F66" s="18"/>
-      <c r="G66" s="19"/>
-      <c r="H66" s="19"/>
-      <c r="I66" s="19"/>
-      <c r="J66" s="20"/>
+      <c r="F66" s="23"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="24"/>
+      <c r="I66" s="24"/>
+      <c r="J66" s="25"/>
     </row>
     <row r="67" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="30"/>
-      <c r="C67" s="31"/>
-      <c r="D67" s="32"/>
+      <c r="B67" s="17"/>
+      <c r="C67" s="18"/>
+      <c r="D67" s="19"/>
       <c r="E67" s="1"/>
-      <c r="F67" s="18"/>
-      <c r="G67" s="19"/>
-      <c r="H67" s="19"/>
-      <c r="I67" s="19"/>
-      <c r="J67" s="20"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="24"/>
+      <c r="H67" s="24"/>
+      <c r="I67" s="24"/>
+      <c r="J67" s="25"/>
     </row>
     <row r="68" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="30"/>
-      <c r="C68" s="31"/>
-      <c r="D68" s="32"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="18"/>
+      <c r="D68" s="19"/>
       <c r="E68" s="1"/>
-      <c r="F68" s="18"/>
-      <c r="G68" s="19"/>
-      <c r="H68" s="19"/>
-      <c r="I68" s="19"/>
-      <c r="J68" s="20"/>
+      <c r="F68" s="23"/>
+      <c r="G68" s="24"/>
+      <c r="H68" s="24"/>
+      <c r="I68" s="24"/>
+      <c r="J68" s="25"/>
     </row>
     <row r="69" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="30"/>
-      <c r="C69" s="31"/>
-      <c r="D69" s="32"/>
+      <c r="B69" s="17"/>
+      <c r="C69" s="18"/>
+      <c r="D69" s="19"/>
       <c r="E69" s="1"/>
-      <c r="F69" s="18"/>
-      <c r="G69" s="19"/>
-      <c r="H69" s="19"/>
-      <c r="I69" s="19"/>
-      <c r="J69" s="20"/>
+      <c r="F69" s="23"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="24"/>
+      <c r="I69" s="24"/>
+      <c r="J69" s="25"/>
     </row>
     <row r="70" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="30"/>
-      <c r="C70" s="31"/>
-      <c r="D70" s="32"/>
+      <c r="B70" s="17"/>
+      <c r="C70" s="18"/>
+      <c r="D70" s="19"/>
       <c r="E70" s="1"/>
-      <c r="F70" s="18"/>
-      <c r="G70" s="19"/>
-      <c r="H70" s="19"/>
-      <c r="I70" s="19"/>
-      <c r="J70" s="20"/>
+      <c r="F70" s="23"/>
+      <c r="G70" s="24"/>
+      <c r="H70" s="24"/>
+      <c r="I70" s="24"/>
+      <c r="J70" s="25"/>
     </row>
     <row r="71" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="30"/>
-      <c r="C71" s="31"/>
-      <c r="D71" s="32"/>
+      <c r="B71" s="17"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="19"/>
       <c r="E71" s="1"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="22"/>
-      <c r="H71" s="22"/>
-      <c r="I71" s="22"/>
-      <c r="J71" s="23"/>
+      <c r="F71" s="26"/>
+      <c r="G71" s="27"/>
+      <c r="H71" s="27"/>
+      <c r="I71" s="27"/>
+      <c r="J71" s="28"/>
     </row>
     <row r="72" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
+      <c r="B72" s="33"/>
+      <c r="C72" s="33"/>
+      <c r="D72" s="33"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
@@ -2000,83 +1971,83 @@
       <c r="J72" s="1"/>
     </row>
     <row r="73" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="12"/>
-      <c r="C73" s="13"/>
-      <c r="D73" s="14"/>
+      <c r="B73" s="29"/>
+      <c r="C73" s="30"/>
+      <c r="D73" s="31"/>
       <c r="E73" s="1"/>
-      <c r="F73" s="15" t="s">
+      <c r="F73" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="G73" s="16"/>
-      <c r="H73" s="16"/>
-      <c r="I73" s="16"/>
-      <c r="J73" s="17"/>
+      <c r="G73" s="21"/>
+      <c r="H73" s="21"/>
+      <c r="I73" s="21"/>
+      <c r="J73" s="22"/>
     </row>
     <row r="74" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="12"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="14"/>
+      <c r="B74" s="29"/>
+      <c r="C74" s="30"/>
+      <c r="D74" s="31"/>
       <c r="E74" s="1"/>
-      <c r="F74" s="18"/>
-      <c r="G74" s="19"/>
-      <c r="H74" s="19"/>
-      <c r="I74" s="19"/>
-      <c r="J74" s="20"/>
+      <c r="F74" s="23"/>
+      <c r="G74" s="24"/>
+      <c r="H74" s="24"/>
+      <c r="I74" s="24"/>
+      <c r="J74" s="25"/>
     </row>
     <row r="75" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="24"/>
-      <c r="C75" s="25"/>
-      <c r="D75" s="26"/>
+      <c r="B75" s="35"/>
+      <c r="C75" s="36"/>
+      <c r="D75" s="37"/>
       <c r="E75" s="1"/>
-      <c r="F75" s="18"/>
-      <c r="G75" s="19"/>
-      <c r="H75" s="19"/>
-      <c r="I75" s="19"/>
-      <c r="J75" s="20"/>
+      <c r="F75" s="23"/>
+      <c r="G75" s="24"/>
+      <c r="H75" s="24"/>
+      <c r="I75" s="24"/>
+      <c r="J75" s="25"/>
     </row>
     <row r="76" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="27"/>
-      <c r="C76" s="28"/>
-      <c r="D76" s="29"/>
+      <c r="B76" s="38"/>
+      <c r="C76" s="39"/>
+      <c r="D76" s="40"/>
       <c r="E76" s="1"/>
-      <c r="F76" s="18"/>
-      <c r="G76" s="19"/>
-      <c r="H76" s="19"/>
-      <c r="I76" s="19"/>
-      <c r="J76" s="20"/>
+      <c r="F76" s="23"/>
+      <c r="G76" s="24"/>
+      <c r="H76" s="24"/>
+      <c r="I76" s="24"/>
+      <c r="J76" s="25"/>
     </row>
     <row r="77" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="27"/>
-      <c r="C77" s="28"/>
-      <c r="D77" s="29"/>
+      <c r="B77" s="38"/>
+      <c r="C77" s="39"/>
+      <c r="D77" s="40"/>
       <c r="E77" s="1"/>
-      <c r="F77" s="18"/>
-      <c r="G77" s="19"/>
-      <c r="H77" s="19"/>
-      <c r="I77" s="19"/>
-      <c r="J77" s="20"/>
+      <c r="F77" s="23"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="24"/>
+      <c r="J77" s="25"/>
     </row>
     <row r="78" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B78" s="27"/>
-      <c r="C78" s="28"/>
-      <c r="D78" s="29"/>
+      <c r="B78" s="38"/>
+      <c r="C78" s="39"/>
+      <c r="D78" s="40"/>
       <c r="E78" s="1"/>
-      <c r="F78" s="18"/>
-      <c r="G78" s="19"/>
-      <c r="H78" s="19"/>
-      <c r="I78" s="19"/>
-      <c r="J78" s="20"/>
+      <c r="F78" s="23"/>
+      <c r="G78" s="24"/>
+      <c r="H78" s="24"/>
+      <c r="I78" s="24"/>
+      <c r="J78" s="25"/>
     </row>
     <row r="79" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="27"/>
-      <c r="C79" s="28"/>
-      <c r="D79" s="29"/>
+      <c r="B79" s="38"/>
+      <c r="C79" s="39"/>
+      <c r="D79" s="40"/>
       <c r="E79" s="1"/>
-      <c r="F79" s="21"/>
-      <c r="G79" s="22"/>
-      <c r="H79" s="22"/>
-      <c r="I79" s="22"/>
-      <c r="J79" s="23"/>
+      <c r="F79" s="26"/>
+      <c r="G79" s="27"/>
+      <c r="H79" s="27"/>
+      <c r="I79" s="27"/>
+      <c r="J79" s="28"/>
     </row>
     <row r="80" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="2"/>
@@ -2112,81 +2083,92 @@
       <c r="J82" s="1"/>
     </row>
     <row r="83" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="7"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="7"/>
+      <c r="B83" s="33"/>
+      <c r="C83" s="33"/>
+      <c r="D83" s="33"/>
       <c r="E83" s="1"/>
-      <c r="F83" s="8"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="8"/>
-      <c r="I83" s="8"/>
+      <c r="F83" s="41"/>
+      <c r="G83" s="41"/>
+      <c r="H83" s="41"/>
+      <c r="I83" s="41"/>
       <c r="J83" s="1"/>
     </row>
     <row r="84" spans="2:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="C84" s="9"/>
-      <c r="D84" s="9"/>
-      <c r="E84" s="9"/>
-      <c r="F84" s="9"/>
-      <c r="G84" s="9"/>
-      <c r="H84" s="9"/>
-      <c r="I84" s="9"/>
-      <c r="J84" s="9"/>
+      <c r="C84" s="42"/>
+      <c r="D84" s="42"/>
+      <c r="E84" s="42"/>
+      <c r="F84" s="42"/>
+      <c r="G84" s="42"/>
+      <c r="H84" s="42"/>
+      <c r="I84" s="42"/>
+      <c r="J84" s="42"/>
       <c r="K84" s="4"/>
     </row>
     <row r="85" spans="2:11" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="10" t="s">
+      <c r="B85" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="C85" s="10"/>
-      <c r="D85" s="10"/>
-      <c r="E85" s="10"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="10"/>
-      <c r="H85" s="10"/>
-      <c r="I85" s="10"/>
-      <c r="J85" s="10"/>
+      <c r="C85" s="43"/>
+      <c r="D85" s="43"/>
+      <c r="E85" s="43"/>
+      <c r="F85" s="43"/>
+      <c r="G85" s="43"/>
+      <c r="H85" s="43"/>
+      <c r="I85" s="43"/>
+      <c r="J85" s="43"/>
       <c r="K85" s="5"/>
     </row>
     <row r="86" spans="2:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="C86" s="11"/>
-      <c r="D86" s="11"/>
-      <c r="E86" s="11"/>
-      <c r="F86" s="11"/>
-      <c r="G86" s="11"/>
-      <c r="H86" s="11"/>
-      <c r="I86" s="11"/>
-      <c r="J86" s="11"/>
+      <c r="C86" s="44"/>
+      <c r="D86" s="44"/>
+      <c r="E86" s="44"/>
+      <c r="F86" s="44"/>
+      <c r="G86" s="44"/>
+      <c r="H86" s="44"/>
+      <c r="I86" s="44"/>
+      <c r="J86" s="44"/>
       <c r="K86" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="69">
-    <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B10:J12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:J20"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E14:E20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:J28"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E22:E28"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="F83:I83"/>
+    <mergeCell ref="B84:J84"/>
+    <mergeCell ref="B85:J85"/>
+    <mergeCell ref="B86:J86"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="F73:J79"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="F65:J71"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B53:J55"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="F57:J63"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B63:D63"/>
     <mergeCell ref="B51:J51"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B30:D30"/>
@@ -2203,38 +2185,27 @@
     <mergeCell ref="B41:J41"/>
     <mergeCell ref="B42:J42"/>
     <mergeCell ref="B43:J43"/>
-    <mergeCell ref="B53:J55"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="F57:J63"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="F65:J71"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="F73:J79"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="F83:I83"/>
-    <mergeCell ref="B84:J84"/>
-    <mergeCell ref="B85:J85"/>
-    <mergeCell ref="B86:J86"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:J28"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E22:E28"/>
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="B10:J12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:J20"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E14:E20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/templates/hemodialysis_list_saloc_template.xlsx
+++ b/templates/hemodialysis_list_saloc_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0FDE45E-40D9-4B8A-A137-16554A863D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6922CCAB-06CE-4782-9529-41D2B9DFAC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0525DECB-4297-493F-802D-35D9B36ABCDF}"/>
   </bookViews>
@@ -627,56 +627,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1263650</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>187616</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>19762</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="Chatveta_04">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D53BAE35-7148-450C-9A93-F72F303B265B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2578100" y="11214100"/>
-          <a:ext cx="193966" cy="2020012"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -998,6 +948,56 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2603500" y="6305550"/>
+          <a:ext cx="193966" cy="2020012"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>200316</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>19762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Chatveta_04">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{219B9B81-656F-41D6-BAB7-B56252F51929}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2590800" y="11214100"/>
           <a:ext cx="193966" cy="2020012"/>
         </a:xfrm>
         <a:prstGeom prst="rect">

--- a/templates/hemodialysis_list_saloc_template.xlsx
+++ b/templates/hemodialysis_list_saloc_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6922CCAB-06CE-4782-9529-41D2B9DFAC16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7578915-BF41-45F9-8605-15910C751FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0525DECB-4297-493F-802D-35D9B36ABCDF}"/>
   </bookViews>
@@ -581,8 +581,8 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
@@ -617,8 +617,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2584450" y="13354050"/>
-          <a:ext cx="193966" cy="2020012"/>
+          <a:off x="2584450" y="13360400"/>
+          <a:ext cx="193966" cy="2013662"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -960,7 +960,7 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>56</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
@@ -968,7 +968,7 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>200316</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>19762</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -997,8 +997,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2590800" y="11214100"/>
-          <a:ext cx="193966" cy="2020012"/>
+          <a:off x="2584450" y="11214100"/>
+          <a:ext cx="200316" cy="2000250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/templates/hemodialysis_list_saloc_template.xlsx
+++ b/templates/hemodialysis_list_saloc_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\CB360-Mobile-main\api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7578915-BF41-45F9-8605-15910C751FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{17A43F72-AC39-467C-823C-3EDC68266BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0525DECB-4297-493F-802D-35D9B36ABCDF}"/>
   </bookViews>
@@ -535,10 +535,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>193966</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>79</xdr:row>
-      <xdr:rowOff>19762</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -568,7 +568,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2584450" y="15506700"/>
-          <a:ext cx="193966" cy="2020012"/>
+          <a:ext cx="222250" cy="2000250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -585,10 +585,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>193966</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>13412</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -618,7 +618,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2584450" y="13360400"/>
-          <a:ext cx="193966" cy="2013662"/>
+          <a:ext cx="222250" cy="2000250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -815,10 +815,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>193966</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>19762</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -848,7 +848,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2584450" y="2019300"/>
-          <a:ext cx="193966" cy="2020012"/>
+          <a:ext cx="222250" cy="2000250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -860,15 +860,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>213016</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>13412</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -897,8 +897,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2603500" y="4159250"/>
-          <a:ext cx="193966" cy="2020012"/>
+          <a:off x="2584450" y="4165600"/>
+          <a:ext cx="222250" cy="2000250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -910,15 +910,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>213016</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>13412</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -947,8 +947,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2603500" y="6305550"/>
-          <a:ext cx="193966" cy="2020012"/>
+          <a:off x="2584450" y="6311900"/>
+          <a:ext cx="222250" cy="2000250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -965,8 +965,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>200316</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>63</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -998,7 +998,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="2584450" y="11214100"/>
-          <a:ext cx="200316" cy="2000250"/>
+          <a:ext cx="222250" cy="2000250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/templates/hemodialysis_list_saloc_template.xlsx
+++ b/templates/hemodialysis_list_saloc_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\CB360-Mobile-main\api\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{17A43F72-AC39-467C-823C-3EDC68266BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7366351C-8FBB-4A5D-9E11-789099285DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0525DECB-4297-493F-802D-35D9B36ABCDF}"/>
   </bookViews>
@@ -373,7 +373,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -477,24 +477,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
@@ -1598,9 +1580,9 @@
       <c r="J31" s="25"/>
     </row>
     <row r="32" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="35"/>
-      <c r="C32" s="36"/>
-      <c r="D32" s="37"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="31"/>
       <c r="E32" s="34"/>
       <c r="F32" s="23"/>
       <c r="G32" s="24"/>
@@ -1609,9 +1591,9 @@
       <c r="J32" s="25"/>
     </row>
     <row r="33" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="38"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="40"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="31"/>
       <c r="E33" s="34"/>
       <c r="F33" s="23"/>
       <c r="G33" s="24"/>
@@ -1620,9 +1602,9 @@
       <c r="J33" s="25"/>
     </row>
     <row r="34" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="38"/>
-      <c r="C34" s="39"/>
-      <c r="D34" s="40"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="30"/>
+      <c r="D34" s="31"/>
       <c r="E34" s="34"/>
       <c r="F34" s="23"/>
       <c r="G34" s="24"/>
@@ -1631,9 +1613,9 @@
       <c r="J34" s="25"/>
     </row>
     <row r="35" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="38"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="40"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="31"/>
       <c r="E35" s="34"/>
       <c r="F35" s="23"/>
       <c r="G35" s="24"/>
@@ -1642,9 +1624,9 @@
       <c r="J35" s="25"/>
     </row>
     <row r="36" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="38"/>
-      <c r="C36" s="39"/>
-      <c r="D36" s="40"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="30"/>
+      <c r="D36" s="31"/>
       <c r="E36" s="34"/>
       <c r="F36" s="26"/>
       <c r="G36" s="27"/>
@@ -1690,52 +1672,52 @@
       <c r="C40" s="33"/>
       <c r="D40" s="33"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="41"/>
-      <c r="I40" s="41"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="2:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="42" t="s">
+      <c r="B41" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C41" s="42"/>
-      <c r="D41" s="42"/>
-      <c r="E41" s="42"/>
-      <c r="F41" s="42"/>
-      <c r="G41" s="42"/>
-      <c r="H41" s="42"/>
-      <c r="I41" s="42"/>
-      <c r="J41" s="42"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="36"/>
+      <c r="J41" s="36"/>
       <c r="K41" s="4"/>
     </row>
     <row r="42" spans="2:11" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="43" t="s">
+      <c r="B42" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="43"/>
-      <c r="D42" s="43"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="43"/>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
+      <c r="C42" s="37"/>
+      <c r="D42" s="37"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="37"/>
+      <c r="I42" s="37"/>
+      <c r="J42" s="37"/>
       <c r="K42" s="5"/>
     </row>
     <row r="43" spans="2:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="44" t="s">
+      <c r="B43" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="44"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="44"/>
-      <c r="H43" s="44"/>
-      <c r="I43" s="44"/>
-      <c r="J43" s="44"/>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="38"/>
+      <c r="J43" s="38"/>
       <c r="K43" s="6"/>
     </row>
     <row r="44" spans="2:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1995,9 +1977,9 @@
       <c r="J74" s="25"/>
     </row>
     <row r="75" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="35"/>
-      <c r="C75" s="36"/>
-      <c r="D75" s="37"/>
+      <c r="B75" s="29"/>
+      <c r="C75" s="30"/>
+      <c r="D75" s="31"/>
       <c r="E75" s="1"/>
       <c r="F75" s="23"/>
       <c r="G75" s="24"/>
@@ -2006,9 +1988,9 @@
       <c r="J75" s="25"/>
     </row>
     <row r="76" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="38"/>
-      <c r="C76" s="39"/>
-      <c r="D76" s="40"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="30"/>
+      <c r="D76" s="31"/>
       <c r="E76" s="1"/>
       <c r="F76" s="23"/>
       <c r="G76" s="24"/>
@@ -2017,9 +1999,9 @@
       <c r="J76" s="25"/>
     </row>
     <row r="77" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="38"/>
-      <c r="C77" s="39"/>
-      <c r="D77" s="40"/>
+      <c r="B77" s="29"/>
+      <c r="C77" s="30"/>
+      <c r="D77" s="31"/>
       <c r="E77" s="1"/>
       <c r="F77" s="23"/>
       <c r="G77" s="24"/>
@@ -2028,9 +2010,9 @@
       <c r="J77" s="25"/>
     </row>
     <row r="78" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B78" s="38"/>
-      <c r="C78" s="39"/>
-      <c r="D78" s="40"/>
+      <c r="B78" s="29"/>
+      <c r="C78" s="30"/>
+      <c r="D78" s="31"/>
       <c r="E78" s="1"/>
       <c r="F78" s="23"/>
       <c r="G78" s="24"/>
@@ -2039,9 +2021,9 @@
       <c r="J78" s="25"/>
     </row>
     <row r="79" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="38"/>
-      <c r="C79" s="39"/>
-      <c r="D79" s="40"/>
+      <c r="B79" s="29"/>
+      <c r="C79" s="30"/>
+      <c r="D79" s="31"/>
       <c r="E79" s="1"/>
       <c r="F79" s="26"/>
       <c r="G79" s="27"/>
@@ -2087,52 +2069,52 @@
       <c r="C83" s="33"/>
       <c r="D83" s="33"/>
       <c r="E83" s="1"/>
-      <c r="F83" s="41"/>
-      <c r="G83" s="41"/>
-      <c r="H83" s="41"/>
-      <c r="I83" s="41"/>
+      <c r="F83" s="35"/>
+      <c r="G83" s="35"/>
+      <c r="H83" s="35"/>
+      <c r="I83" s="35"/>
       <c r="J83" s="1"/>
     </row>
     <row r="84" spans="2:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="42" t="s">
+      <c r="B84" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="C84" s="42"/>
-      <c r="D84" s="42"/>
-      <c r="E84" s="42"/>
-      <c r="F84" s="42"/>
-      <c r="G84" s="42"/>
-      <c r="H84" s="42"/>
-      <c r="I84" s="42"/>
-      <c r="J84" s="42"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+      <c r="G84" s="36"/>
+      <c r="H84" s="36"/>
+      <c r="I84" s="36"/>
+      <c r="J84" s="36"/>
       <c r="K84" s="4"/>
     </row>
     <row r="85" spans="2:11" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="43" t="s">
+      <c r="B85" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="C85" s="43"/>
-      <c r="D85" s="43"/>
-      <c r="E85" s="43"/>
-      <c r="F85" s="43"/>
-      <c r="G85" s="43"/>
-      <c r="H85" s="43"/>
-      <c r="I85" s="43"/>
-      <c r="J85" s="43"/>
+      <c r="C85" s="37"/>
+      <c r="D85" s="37"/>
+      <c r="E85" s="37"/>
+      <c r="F85" s="37"/>
+      <c r="G85" s="37"/>
+      <c r="H85" s="37"/>
+      <c r="I85" s="37"/>
+      <c r="J85" s="37"/>
       <c r="K85" s="5"/>
     </row>
     <row r="86" spans="2:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="44" t="s">
+      <c r="B86" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="C86" s="44"/>
-      <c r="D86" s="44"/>
-      <c r="E86" s="44"/>
-      <c r="F86" s="44"/>
-      <c r="G86" s="44"/>
-      <c r="H86" s="44"/>
-      <c r="I86" s="44"/>
-      <c r="J86" s="44"/>
+      <c r="C86" s="38"/>
+      <c r="D86" s="38"/>
+      <c r="E86" s="38"/>
+      <c r="F86" s="38"/>
+      <c r="G86" s="38"/>
+      <c r="H86" s="38"/>
+      <c r="I86" s="38"/>
+      <c r="J86" s="38"/>
       <c r="K86" s="6"/>
     </row>
   </sheetData>

--- a/templates/hemodialysis_list_saloc_template.xlsx
+++ b/templates/hemodialysis_list_saloc_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7366351C-8FBB-4A5D-9E11-789099285DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C109D0B-CC43-48E5-837A-ABC41023BB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0525DECB-4297-493F-802D-35D9B36ABCDF}"/>
+    <workbookView xWindow="2460" yWindow="2460" windowWidth="21600" windowHeight="11385" xr2:uid="{0525DECB-4297-493F-802D-35D9B36ABCDF}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -153,7 +153,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -358,22 +358,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -391,35 +380,74 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -433,62 +461,35 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,25 +510,20 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>194862</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>90475</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="4850210" cy="102077"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Chatveta_06">
+        <xdr:cNvPr id="3" name="Imagem 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B536E5F-4F31-4447-8EBD-B0049ADBE6CB}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A04273E-86DB-4790-9C62-5235C7FA2BE4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -549,8 +545,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2584450" y="15506700"/>
-          <a:ext cx="222250" cy="2000250"/>
+          <a:off x="899712" y="17883175"/>
+          <a:ext cx="4850210" cy="102077"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -558,26 +554,21 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>194862</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>90475</xdr:rowOff>
     </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
+    <xdr:ext cx="4850210" cy="102077"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Chatveta_05">
+        <xdr:cNvPr id="2" name="Imagem 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0E89DE2E-22CC-47B6-8E07-BB3173BA6B10}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54D278EF-4F7E-4AD1-BB26-DAB43E5786ED}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -599,8 +590,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2584450" y="13360400"/>
-          <a:ext cx="222250" cy="2000250"/>
+          <a:off x="899712" y="8688375"/>
+          <a:ext cx="4850210" cy="102077"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -608,7 +599,7 @@
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
-  </xdr:twoCellAnchor>
+  </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -654,10 +645,199 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1363265</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>180000</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Chaveta à direita 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD6A866B-BCF9-4884-BECE-6E251B8B0093}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2582465" y="13725526"/>
+          <a:ext cx="178810" cy="2000250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightBrace">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1363265</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>180000</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="Chaveta à direita 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3340CCAE-25C4-4A74-A7ED-5A342D4C307E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2582465" y="15868650"/>
+          <a:ext cx="178810" cy="2000250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightBrace">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>186350</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>333375</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="Chaveta à direita 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDE35191-7EAD-4B41-85FF-67600AFC43D1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2587625" y="11582400"/>
+          <a:ext cx="180000" cy="2000250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightBrace">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>448862</xdr:colOff>
+      <xdr:colOff>4362</xdr:colOff>
       <xdr:row>82</xdr:row>
       <xdr:rowOff>90475</xdr:rowOff>
     </xdr:from>
@@ -676,7 +856,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -689,7 +869,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="544112" y="17883175"/>
+          <a:off x="99612" y="17883175"/>
           <a:ext cx="4850210" cy="102077"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -699,10 +879,199 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1363265</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>180000</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Chaveta à direita 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A17630A5-8323-4FDA-B65F-DC2402B45832}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2582465" y="4114801"/>
+          <a:ext cx="178810" cy="2000250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightBrace">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>1363265</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>180000</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Chaveta à direita 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BDFA0FDC-06C8-4874-AB82-42BFD314E72E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2582465" y="6257925"/>
+          <a:ext cx="178810" cy="2000250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightBrace">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>6350</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>186350</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>333375</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Chaveta à direita 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14A3F533-C097-47AA-9CCA-23DB2AC51DFE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2587625" y="1971675"/>
+          <a:ext cx="180000" cy="2000250"/>
+        </a:xfrm>
+        <a:prstGeom prst="rightBrace">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050">
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-PT" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>448862</xdr:colOff>
+      <xdr:colOff>4362</xdr:colOff>
       <xdr:row>39</xdr:row>
       <xdr:rowOff>90475</xdr:rowOff>
     </xdr:from>
@@ -721,7 +1090,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -734,7 +1103,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="544112" y="8688375"/>
+          <a:off x="99612" y="8688375"/>
           <a:ext cx="4850210" cy="102077"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -789,206 +1158,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Chatveta_01">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AD5D157-C7DF-9B08-27F5-6B698ABD70A0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2584450" y="2019300"/>
-          <a:ext cx="222250" cy="2000250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Chatveta_02">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6D8C5EB4-9652-46D2-93E3-B7A615FE51C7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2584450" y="4165600"/>
-          <a:ext cx="222250" cy="2000250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Chatveta_03">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B042A2A-D74F-45D0-8D75-BC92055D8E00}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2584450" y="6311900"/>
-          <a:ext cx="222250" cy="2000250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Chatveta_04">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{219B9B81-656F-41D6-BAB7-B56252F51929}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2584450" y="11214100"/>
-          <a:ext cx="222250" cy="2000250"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1326,138 +1495,138 @@
     <row r="1" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="7" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
     </row>
     <row r="9" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="10"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="35"/>
     </row>
     <row r="11" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="11"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="13"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="38"/>
     </row>
     <row r="12" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="14"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="16"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="40"/>
+      <c r="I12" s="40"/>
+      <c r="J12" s="41"/>
     </row>
     <row r="13" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="17"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="20" t="s">
+    <row r="14" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="30"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="22"/>
-    </row>
-    <row r="15" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="17"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="25"/>
-    </row>
-    <row r="16" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="17"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="23"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="25"/>
-    </row>
-    <row r="17" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="17"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="25"/>
-    </row>
-    <row r="18" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="17"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="23"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="25"/>
-    </row>
-    <row r="19" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="17"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="25"/>
-    </row>
-    <row r="20" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="29"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="28"/>
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="17"/>
+    </row>
+    <row r="15" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B15" s="30"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="20"/>
+    </row>
+    <row r="16" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="30"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="20"/>
+    </row>
+    <row r="17" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B18" s="30"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="20"/>
+    </row>
+    <row r="19" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B19" s="30"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="20"/>
+    </row>
+    <row r="20" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B20" s="12"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
+      <c r="J20" s="23"/>
     </row>
     <row r="21" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="33"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -1465,89 +1634,89 @@
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
     </row>
-    <row r="22" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="17"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="20" t="s">
+    <row r="22" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="22"/>
-    </row>
-    <row r="23" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="17"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="25"/>
-    </row>
-    <row r="24" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="17"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="34"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="25"/>
-    </row>
-    <row r="25" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="17"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="34"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="24"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="25"/>
-    </row>
-    <row r="26" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="17"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="34"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="25"/>
-    </row>
-    <row r="27" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="17"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="25"/>
-    </row>
-    <row r="28" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="17"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="26"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="28"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="17"/>
+    </row>
+    <row r="23" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="18"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="20"/>
+    </row>
+    <row r="24" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="30"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="20"/>
+    </row>
+    <row r="25" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="30"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="20"/>
+    </row>
+    <row r="26" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="30"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="20"/>
+    </row>
+    <row r="27" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="30"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="20"/>
+    </row>
+    <row r="28" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="30"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
+      <c r="J28" s="23"/>
     </row>
     <row r="29" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="33"/>
-      <c r="C29" s="33"/>
-      <c r="D29" s="33"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -1555,84 +1724,84 @@
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
     </row>
-    <row r="30" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="29"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="20" t="s">
+    <row r="30" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="12"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
-      <c r="J30" s="22"/>
-    </row>
-    <row r="31" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="29"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="23"/>
-      <c r="G31" s="24"/>
-      <c r="H31" s="24"/>
-      <c r="I31" s="24"/>
-      <c r="J31" s="25"/>
-    </row>
-    <row r="32" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="29"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="23"/>
-      <c r="G32" s="24"/>
-      <c r="H32" s="24"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="25"/>
-    </row>
-    <row r="33" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="29"/>
-      <c r="C33" s="30"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="23"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="25"/>
-    </row>
-    <row r="34" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="29"/>
-      <c r="C34" s="30"/>
-      <c r="D34" s="31"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="24"/>
-      <c r="H34" s="24"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="25"/>
-    </row>
-    <row r="35" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="29"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="31"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="24"/>
-      <c r="H35" s="24"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="25"/>
-    </row>
-    <row r="36" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="29"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="31"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="26"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="28"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="16"/>
+      <c r="I30" s="16"/>
+      <c r="J30" s="17"/>
+    </row>
+    <row r="31" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="12"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="20"/>
+    </row>
+    <row r="32" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="24"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="20"/>
+    </row>
+    <row r="33" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="27"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="20"/>
+    </row>
+    <row r="34" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="27"/>
+      <c r="C34" s="28"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="20"/>
+    </row>
+    <row r="35" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="27"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="29"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="20"/>
+    </row>
+    <row r="36" spans="2:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="27"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="21"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="22"/>
+      <c r="I36" s="22"/>
+      <c r="J36" s="23"/>
     </row>
     <row r="37" spans="2:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="2"/>
@@ -1668,193 +1837,193 @@
       <c r="J39" s="1"/>
     </row>
     <row r="40" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="33"/>
-      <c r="C40" s="33"/>
-      <c r="D40" s="33"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
       <c r="E40" s="1"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="35"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="35"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
       <c r="J40" s="1"/>
     </row>
     <row r="41" spans="2:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="36" t="s">
+      <c r="B41" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="36"/>
-      <c r="F41" s="36"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="36"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="36"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
       <c r="K41" s="4"/>
     </row>
     <row r="42" spans="2:11" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="37" t="s">
+      <c r="B42" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="37"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="37"/>
-      <c r="H42" s="37"/>
-      <c r="I42" s="37"/>
-      <c r="J42" s="37"/>
+      <c r="C42" s="10"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
       <c r="K42" s="5"/>
     </row>
     <row r="43" spans="2:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="38" t="s">
+      <c r="B43" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="38"/>
-      <c r="D43" s="38"/>
-      <c r="E43" s="38"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="38"/>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
-      <c r="J43" s="38"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
       <c r="K43" s="6"/>
     </row>
     <row r="44" spans="2:11" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
+      <c r="C51" s="42"/>
+      <c r="D51" s="42"/>
+      <c r="E51" s="42"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="42"/>
+      <c r="H51" s="42"/>
+      <c r="I51" s="42"/>
+      <c r="J51" s="42"/>
     </row>
     <row r="52" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="53" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="9"/>
-      <c r="H53" s="9"/>
-      <c r="I53" s="9"/>
-      <c r="J53" s="10"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="34"/>
+      <c r="I53" s="34"/>
+      <c r="J53" s="35"/>
     </row>
     <row r="54" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="11"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="13"/>
+      <c r="B54" s="36"/>
+      <c r="C54" s="37"/>
+      <c r="D54" s="37"/>
+      <c r="E54" s="37"/>
+      <c r="F54" s="37"/>
+      <c r="G54" s="37"/>
+      <c r="H54" s="37"/>
+      <c r="I54" s="37"/>
+      <c r="J54" s="38"/>
     </row>
     <row r="55" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="14"/>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15"/>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15"/>
-      <c r="H55" s="15"/>
-      <c r="I55" s="15"/>
-      <c r="J55" s="16"/>
+      <c r="B55" s="39"/>
+      <c r="C55" s="40"/>
+      <c r="D55" s="40"/>
+      <c r="E55" s="40"/>
+      <c r="F55" s="40"/>
+      <c r="G55" s="40"/>
+      <c r="H55" s="40"/>
+      <c r="I55" s="40"/>
+      <c r="J55" s="41"/>
     </row>
     <row r="56" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="57" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B57" s="17"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="19"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="31"/>
+      <c r="D57" s="32"/>
       <c r="E57" s="1"/>
-      <c r="F57" s="20" t="s">
+      <c r="F57" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="G57" s="21"/>
-      <c r="H57" s="21"/>
-      <c r="I57" s="21"/>
-      <c r="J57" s="22"/>
+      <c r="G57" s="16"/>
+      <c r="H57" s="16"/>
+      <c r="I57" s="16"/>
+      <c r="J57" s="17"/>
     </row>
     <row r="58" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B58" s="17"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="19"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="32"/>
       <c r="E58" s="1"/>
-      <c r="F58" s="23"/>
-      <c r="G58" s="24"/>
-      <c r="H58" s="24"/>
-      <c r="I58" s="24"/>
-      <c r="J58" s="25"/>
+      <c r="F58" s="18"/>
+      <c r="G58" s="19"/>
+      <c r="H58" s="19"/>
+      <c r="I58" s="19"/>
+      <c r="J58" s="20"/>
     </row>
     <row r="59" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B59" s="17"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="19"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="32"/>
       <c r="E59" s="1"/>
-      <c r="F59" s="23"/>
-      <c r="G59" s="24"/>
-      <c r="H59" s="24"/>
-      <c r="I59" s="24"/>
-      <c r="J59" s="25"/>
+      <c r="F59" s="18"/>
+      <c r="G59" s="19"/>
+      <c r="H59" s="19"/>
+      <c r="I59" s="19"/>
+      <c r="J59" s="20"/>
     </row>
     <row r="60" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="17"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="19"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="31"/>
+      <c r="D60" s="32"/>
       <c r="E60" s="1"/>
-      <c r="F60" s="23"/>
-      <c r="G60" s="24"/>
-      <c r="H60" s="24"/>
-      <c r="I60" s="24"/>
-      <c r="J60" s="25"/>
+      <c r="F60" s="18"/>
+      <c r="G60" s="19"/>
+      <c r="H60" s="19"/>
+      <c r="I60" s="19"/>
+      <c r="J60" s="20"/>
     </row>
     <row r="61" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="17"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="19"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="32"/>
       <c r="E61" s="1"/>
-      <c r="F61" s="23"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="24"/>
-      <c r="I61" s="24"/>
-      <c r="J61" s="25"/>
+      <c r="F61" s="18"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="20"/>
     </row>
     <row r="62" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="17"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="19"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="31"/>
+      <c r="D62" s="32"/>
       <c r="E62" s="1"/>
-      <c r="F62" s="23"/>
-      <c r="G62" s="24"/>
-      <c r="H62" s="24"/>
-      <c r="I62" s="24"/>
-      <c r="J62" s="25"/>
+      <c r="F62" s="18"/>
+      <c r="G62" s="19"/>
+      <c r="H62" s="19"/>
+      <c r="I62" s="19"/>
+      <c r="J62" s="20"/>
     </row>
     <row r="63" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="29"/>
-      <c r="C63" s="30"/>
-      <c r="D63" s="31"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="13"/>
+      <c r="D63" s="14"/>
       <c r="E63" s="1"/>
-      <c r="F63" s="26"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="27"/>
-      <c r="I63" s="27"/>
-      <c r="J63" s="28"/>
+      <c r="F63" s="21"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="23"/>
     </row>
     <row r="64" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="33"/>
-      <c r="C64" s="33"/>
-      <c r="D64" s="33"/>
+      <c r="B64" s="7"/>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -1863,88 +2032,88 @@
       <c r="J64" s="1"/>
     </row>
     <row r="65" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="17"/>
-      <c r="C65" s="18"/>
-      <c r="D65" s="19"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="31"/>
+      <c r="D65" s="32"/>
       <c r="E65" s="1"/>
-      <c r="F65" s="20" t="s">
+      <c r="F65" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="G65" s="21"/>
-      <c r="H65" s="21"/>
-      <c r="I65" s="21"/>
-      <c r="J65" s="22"/>
+      <c r="G65" s="16"/>
+      <c r="H65" s="16"/>
+      <c r="I65" s="16"/>
+      <c r="J65" s="17"/>
     </row>
     <row r="66" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="17"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="19"/>
+      <c r="B66" s="30"/>
+      <c r="C66" s="31"/>
+      <c r="D66" s="32"/>
       <c r="E66" s="1"/>
-      <c r="F66" s="23"/>
-      <c r="G66" s="24"/>
-      <c r="H66" s="24"/>
-      <c r="I66" s="24"/>
-      <c r="J66" s="25"/>
+      <c r="F66" s="18"/>
+      <c r="G66" s="19"/>
+      <c r="H66" s="19"/>
+      <c r="I66" s="19"/>
+      <c r="J66" s="20"/>
     </row>
     <row r="67" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="17"/>
-      <c r="C67" s="18"/>
-      <c r="D67" s="19"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="32"/>
       <c r="E67" s="1"/>
-      <c r="F67" s="23"/>
-      <c r="G67" s="24"/>
-      <c r="H67" s="24"/>
-      <c r="I67" s="24"/>
-      <c r="J67" s="25"/>
+      <c r="F67" s="18"/>
+      <c r="G67" s="19"/>
+      <c r="H67" s="19"/>
+      <c r="I67" s="19"/>
+      <c r="J67" s="20"/>
     </row>
     <row r="68" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="17"/>
-      <c r="C68" s="18"/>
-      <c r="D68" s="19"/>
+      <c r="B68" s="30"/>
+      <c r="C68" s="31"/>
+      <c r="D68" s="32"/>
       <c r="E68" s="1"/>
-      <c r="F68" s="23"/>
-      <c r="G68" s="24"/>
-      <c r="H68" s="24"/>
-      <c r="I68" s="24"/>
-      <c r="J68" s="25"/>
+      <c r="F68" s="18"/>
+      <c r="G68" s="19"/>
+      <c r="H68" s="19"/>
+      <c r="I68" s="19"/>
+      <c r="J68" s="20"/>
     </row>
     <row r="69" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="17"/>
-      <c r="C69" s="18"/>
-      <c r="D69" s="19"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="32"/>
       <c r="E69" s="1"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="24"/>
-      <c r="H69" s="24"/>
-      <c r="I69" s="24"/>
-      <c r="J69" s="25"/>
+      <c r="F69" s="18"/>
+      <c r="G69" s="19"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
+      <c r="J69" s="20"/>
     </row>
     <row r="70" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="17"/>
-      <c r="C70" s="18"/>
-      <c r="D70" s="19"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="32"/>
       <c r="E70" s="1"/>
-      <c r="F70" s="23"/>
-      <c r="G70" s="24"/>
-      <c r="H70" s="24"/>
-      <c r="I70" s="24"/>
-      <c r="J70" s="25"/>
+      <c r="F70" s="18"/>
+      <c r="G70" s="19"/>
+      <c r="H70" s="19"/>
+      <c r="I70" s="19"/>
+      <c r="J70" s="20"/>
     </row>
     <row r="71" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="17"/>
-      <c r="C71" s="18"/>
-      <c r="D71" s="19"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="31"/>
+      <c r="D71" s="32"/>
       <c r="E71" s="1"/>
-      <c r="F71" s="26"/>
-      <c r="G71" s="27"/>
-      <c r="H71" s="27"/>
-      <c r="I71" s="27"/>
-      <c r="J71" s="28"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="22"/>
+      <c r="J71" s="23"/>
     </row>
     <row r="72" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="33"/>
-      <c r="C72" s="33"/>
-      <c r="D72" s="33"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="7"/>
+      <c r="D72" s="7"/>
       <c r="E72" s="1"/>
       <c r="F72" s="1"/>
       <c r="G72" s="1"/>
@@ -1953,83 +2122,83 @@
       <c r="J72" s="1"/>
     </row>
     <row r="73" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="29"/>
-      <c r="C73" s="30"/>
-      <c r="D73" s="31"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="13"/>
+      <c r="D73" s="14"/>
       <c r="E73" s="1"/>
-      <c r="F73" s="20" t="s">
+      <c r="F73" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21"/>
-      <c r="J73" s="22"/>
+      <c r="G73" s="16"/>
+      <c r="H73" s="16"/>
+      <c r="I73" s="16"/>
+      <c r="J73" s="17"/>
     </row>
     <row r="74" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="29"/>
-      <c r="C74" s="30"/>
-      <c r="D74" s="31"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="14"/>
       <c r="E74" s="1"/>
-      <c r="F74" s="23"/>
-      <c r="G74" s="24"/>
-      <c r="H74" s="24"/>
-      <c r="I74" s="24"/>
-      <c r="J74" s="25"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="19"/>
+      <c r="H74" s="19"/>
+      <c r="I74" s="19"/>
+      <c r="J74" s="20"/>
     </row>
     <row r="75" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="29"/>
-      <c r="C75" s="30"/>
-      <c r="D75" s="31"/>
+      <c r="B75" s="24"/>
+      <c r="C75" s="25"/>
+      <c r="D75" s="26"/>
       <c r="E75" s="1"/>
-      <c r="F75" s="23"/>
-      <c r="G75" s="24"/>
-      <c r="H75" s="24"/>
-      <c r="I75" s="24"/>
-      <c r="J75" s="25"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="19"/>
+      <c r="H75" s="19"/>
+      <c r="I75" s="19"/>
+      <c r="J75" s="20"/>
     </row>
     <row r="76" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B76" s="29"/>
-      <c r="C76" s="30"/>
-      <c r="D76" s="31"/>
+      <c r="B76" s="27"/>
+      <c r="C76" s="28"/>
+      <c r="D76" s="29"/>
       <c r="E76" s="1"/>
-      <c r="F76" s="23"/>
-      <c r="G76" s="24"/>
-      <c r="H76" s="24"/>
-      <c r="I76" s="24"/>
-      <c r="J76" s="25"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="19"/>
+      <c r="H76" s="19"/>
+      <c r="I76" s="19"/>
+      <c r="J76" s="20"/>
     </row>
     <row r="77" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B77" s="29"/>
-      <c r="C77" s="30"/>
-      <c r="D77" s="31"/>
+      <c r="B77" s="27"/>
+      <c r="C77" s="28"/>
+      <c r="D77" s="29"/>
       <c r="E77" s="1"/>
-      <c r="F77" s="23"/>
-      <c r="G77" s="24"/>
-      <c r="H77" s="24"/>
-      <c r="I77" s="24"/>
-      <c r="J77" s="25"/>
+      <c r="F77" s="18"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
+      <c r="I77" s="19"/>
+      <c r="J77" s="20"/>
     </row>
     <row r="78" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B78" s="29"/>
-      <c r="C78" s="30"/>
-      <c r="D78" s="31"/>
+      <c r="B78" s="27"/>
+      <c r="C78" s="28"/>
+      <c r="D78" s="29"/>
       <c r="E78" s="1"/>
-      <c r="F78" s="23"/>
-      <c r="G78" s="24"/>
-      <c r="H78" s="24"/>
-      <c r="I78" s="24"/>
-      <c r="J78" s="25"/>
+      <c r="F78" s="18"/>
+      <c r="G78" s="19"/>
+      <c r="H78" s="19"/>
+      <c r="I78" s="19"/>
+      <c r="J78" s="20"/>
     </row>
     <row r="79" spans="2:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B79" s="29"/>
-      <c r="C79" s="30"/>
-      <c r="D79" s="31"/>
+      <c r="B79" s="27"/>
+      <c r="C79" s="28"/>
+      <c r="D79" s="29"/>
       <c r="E79" s="1"/>
-      <c r="F79" s="26"/>
-      <c r="G79" s="27"/>
-      <c r="H79" s="27"/>
-      <c r="I79" s="27"/>
-      <c r="J79" s="28"/>
+      <c r="F79" s="21"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="22"/>
+      <c r="J79" s="23"/>
     </row>
     <row r="80" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B80" s="2"/>
@@ -2065,92 +2234,79 @@
       <c r="J82" s="1"/>
     </row>
     <row r="83" spans="2:11" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B83" s="33"/>
-      <c r="C83" s="33"/>
-      <c r="D83" s="33"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
       <c r="E83" s="1"/>
-      <c r="F83" s="35"/>
-      <c r="G83" s="35"/>
-      <c r="H83" s="35"/>
-      <c r="I83" s="35"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="8"/>
+      <c r="I83" s="8"/>
       <c r="J83" s="1"/>
     </row>
     <row r="84" spans="2:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="36" t="s">
+      <c r="B84" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C84" s="36"/>
-      <c r="D84" s="36"/>
-      <c r="E84" s="36"/>
-      <c r="F84" s="36"/>
-      <c r="G84" s="36"/>
-      <c r="H84" s="36"/>
-      <c r="I84" s="36"/>
-      <c r="J84" s="36"/>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9"/>
+      <c r="E84" s="9"/>
+      <c r="F84" s="9"/>
+      <c r="G84" s="9"/>
+      <c r="H84" s="9"/>
+      <c r="I84" s="9"/>
+      <c r="J84" s="9"/>
       <c r="K84" s="4"/>
     </row>
     <row r="85" spans="2:11" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="37" t="s">
+      <c r="B85" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C85" s="37"/>
-      <c r="D85" s="37"/>
-      <c r="E85" s="37"/>
-      <c r="F85" s="37"/>
-      <c r="G85" s="37"/>
-      <c r="H85" s="37"/>
-      <c r="I85" s="37"/>
-      <c r="J85" s="37"/>
+      <c r="C85" s="10"/>
+      <c r="D85" s="10"/>
+      <c r="E85" s="10"/>
+      <c r="F85" s="10"/>
+      <c r="G85" s="10"/>
+      <c r="H85" s="10"/>
+      <c r="I85" s="10"/>
+      <c r="J85" s="10"/>
       <c r="K85" s="5"/>
     </row>
     <row r="86" spans="2:11" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="38" t="s">
+      <c r="B86" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C86" s="38"/>
-      <c r="D86" s="38"/>
-      <c r="E86" s="38"/>
-      <c r="F86" s="38"/>
-      <c r="G86" s="38"/>
-      <c r="H86" s="38"/>
-      <c r="I86" s="38"/>
-      <c r="J86" s="38"/>
+      <c r="C86" s="11"/>
+      <c r="D86" s="11"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="11"/>
+      <c r="G86" s="11"/>
+      <c r="H86" s="11"/>
+      <c r="I86" s="11"/>
+      <c r="J86" s="11"/>
       <c r="K86" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="69">
-    <mergeCell ref="B83:D83"/>
-    <mergeCell ref="F83:I83"/>
-    <mergeCell ref="B84:J84"/>
-    <mergeCell ref="B85:J85"/>
-    <mergeCell ref="B86:J86"/>
-    <mergeCell ref="B72:D72"/>
-    <mergeCell ref="B73:D73"/>
-    <mergeCell ref="F73:J79"/>
-    <mergeCell ref="B74:D74"/>
-    <mergeCell ref="B75:D75"/>
-    <mergeCell ref="B76:D76"/>
-    <mergeCell ref="B77:D77"/>
-    <mergeCell ref="B78:D78"/>
-    <mergeCell ref="B79:D79"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="F65:J71"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B69:D69"/>
-    <mergeCell ref="B70:D70"/>
-    <mergeCell ref="B71:D71"/>
-    <mergeCell ref="B53:J55"/>
-    <mergeCell ref="B57:D57"/>
-    <mergeCell ref="F57:J63"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="B59:D59"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="B63:D63"/>
+  <mergeCells count="66">
+    <mergeCell ref="B8:J8"/>
+    <mergeCell ref="B10:J12"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:J20"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="F22:J28"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="B51:J51"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B30:D30"/>
@@ -2161,33 +2317,43 @@
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B36:D36"/>
-    <mergeCell ref="E30:E36"/>
     <mergeCell ref="B40:D40"/>
     <mergeCell ref="F40:I40"/>
     <mergeCell ref="B41:J41"/>
     <mergeCell ref="B42:J42"/>
     <mergeCell ref="B43:J43"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:J28"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E22:E28"/>
-    <mergeCell ref="B8:J8"/>
-    <mergeCell ref="B10:J12"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:J20"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E14:E20"/>
+    <mergeCell ref="B53:J55"/>
+    <mergeCell ref="B57:D57"/>
+    <mergeCell ref="F57:J63"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="F65:J71"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B69:D69"/>
+    <mergeCell ref="B70:D70"/>
+    <mergeCell ref="B71:D71"/>
+    <mergeCell ref="B72:D72"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="F73:J79"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B78:D78"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="B83:D83"/>
+    <mergeCell ref="F83:I83"/>
+    <mergeCell ref="B84:J84"/>
+    <mergeCell ref="B85:J85"/>
+    <mergeCell ref="B86:J86"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
